--- a/research/traditional_assets/database/data/oman/oman_telecom_wireless.xlsx
+++ b/research/traditional_assets/database/data/oman/oman_telecom_wireless.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.09461647217374622</v>
+        <v>0.09453999746548561</v>
       </c>
       <c r="C2">
-        <v>539.4098302523076</v>
+        <v>534.5860740724362</v>
       </c>
       <c r="D2">
-        <v>533.1898302523076</v>
+        <v>533.6000740724362</v>
       </c>
       <c r="E2">
-        <v>-134.5</v>
+        <v>-129.266</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>5.234</v>
       </c>
       <c r="G2">
         <v>6.22</v>
@@ -1451,45 +1451,45 @@
         <v>2.177777777777806</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.280019</v>
       </c>
       <c r="N2">
-        <v>2.177777777777806</v>
+        <v>1.897758777777806</v>
       </c>
       <c r="O2">
-        <v>0.3266666666666708</v>
+        <v>0.2846638166666708</v>
       </c>
       <c r="P2">
-        <v>1.851111111111135</v>
+        <v>1.613094961111135</v>
       </c>
       <c r="Q2">
-        <v>174.4511111111111</v>
+        <v>174.2130949611111</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.09461647217374622</v>
+        <v>0.09503560350049051</v>
       </c>
       <c r="T2">
-        <v>0.6362422799549506</v>
+        <v>0.641704966196988</v>
       </c>
       <c r="U2">
-        <v>0.0503</v>
+        <v>0.0535</v>
       </c>
       <c r="V2">
         <v>0.15</v>
       </c>
       <c r="W2">
-        <v>0.04275499999999999</v>
+        <v>0.04547499999999999</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>7.777250035811161</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.09453999746548561</v>
+        <v>0.09464372275722499</v>
       </c>
       <c r="C3">
-        <v>534.5860740724362</v>
+        <v>528.7957985868316</v>
       </c>
       <c r="D3">
-        <v>533.6000740724362</v>
+        <v>533.0437985868315</v>
       </c>
       <c r="E3">
-        <v>-129.266</v>
+        <v>-124.032</v>
       </c>
       <c r="F3">
-        <v>5.234</v>
+        <v>10.468</v>
       </c>
       <c r="G3">
         <v>6.22</v>
@@ -1533,45 +1533,45 @@
         <v>2.177777777777806</v>
       </c>
       <c r="M3">
-        <v>0.280019</v>
+        <v>0.6709988</v>
       </c>
       <c r="N3">
-        <v>1.897758777777806</v>
+        <v>1.506778977777806</v>
       </c>
       <c r="O3">
-        <v>0.2846638166666708</v>
+        <v>0.2260168466666708</v>
       </c>
       <c r="P3">
-        <v>1.613094961111135</v>
+        <v>1.280762131111135</v>
       </c>
       <c r="Q3">
-        <v>174.2130949611111</v>
+        <v>173.8807621311111</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.09503560350049051</v>
+        <v>0.0954632885277806</v>
       </c>
       <c r="T3">
-        <v>0.641704966196988</v>
+        <v>0.6472791358317203</v>
       </c>
       <c r="U3">
-        <v>0.0535</v>
+        <v>0.0641</v>
       </c>
       <c r="V3">
         <v>0.15</v>
       </c>
       <c r="W3">
-        <v>0.04547499999999999</v>
+        <v>0.054485</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y3">
-        <v>7.777250035811161</v>
+        <v>3.245576262994518</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.09464372275722499</v>
+        <v>0.09531779804896437</v>
       </c>
       <c r="C4">
-        <v>528.7957985868316</v>
+        <v>519.9748237206455</v>
       </c>
       <c r="D4">
-        <v>533.0437985868315</v>
+        <v>529.4568237206455</v>
       </c>
       <c r="E4">
-        <v>-124.032</v>
+        <v>-118.798</v>
       </c>
       <c r="F4">
-        <v>10.468</v>
+        <v>15.702</v>
       </c>
       <c r="G4">
         <v>6.22</v>
@@ -1615,45 +1615,45 @@
         <v>2.177777777777806</v>
       </c>
       <c r="M4">
-        <v>0.6709988</v>
+        <v>1.41318</v>
       </c>
       <c r="N4">
-        <v>1.506778977777806</v>
+        <v>0.7645977777778057</v>
       </c>
       <c r="O4">
-        <v>0.2260168466666708</v>
+        <v>0.1146896666666709</v>
       </c>
       <c r="P4">
-        <v>1.280762131111135</v>
+        <v>0.6499081111111349</v>
       </c>
       <c r="Q4">
-        <v>173.8807621311111</v>
+        <v>173.2499081111111</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.0954632885277806</v>
+        <v>0.09589979180305605</v>
       </c>
       <c r="T4">
-        <v>0.6472791358317203</v>
+        <v>0.6529682367991271</v>
       </c>
       <c r="U4">
-        <v>0.0641</v>
+        <v>0.09</v>
       </c>
       <c r="V4">
         <v>0.15</v>
       </c>
       <c r="W4">
-        <v>0.054485</v>
+        <v>0.0765</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y4">
-        <v>3.245576262994518</v>
+        <v>1.541047692281101</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.09531779804896437</v>
+        <v>0.1000406170452528</v>
       </c>
       <c r="C5">
-        <v>519.9748237206455</v>
+        <v>490.9022078033032</v>
       </c>
       <c r="D5">
-        <v>529.4568237206455</v>
+        <v>505.6182078033031</v>
       </c>
       <c r="E5">
-        <v>-118.798</v>
+        <v>-113.564</v>
       </c>
       <c r="F5">
-        <v>15.702</v>
+        <v>20.936</v>
       </c>
       <c r="G5">
         <v>6.22</v>
@@ -1697,45 +1697,45 @@
         <v>2.177777777777806</v>
       </c>
       <c r="M5">
-        <v>1.41318</v>
+        <v>4.2039488</v>
       </c>
       <c r="N5">
-        <v>0.7645977777778057</v>
+        <v>-2.026171022222194</v>
       </c>
       <c r="O5">
-        <v>0.1146896666666709</v>
+        <v>-0.3039256533333292</v>
       </c>
       <c r="P5">
-        <v>0.6499081111111349</v>
+        <v>-1.722245368888865</v>
       </c>
       <c r="Q5">
-        <v>173.2499081111111</v>
+        <v>170.8777546311111</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.09589979180305605</v>
+        <v>0.09649243891731946</v>
       </c>
       <c r="T5">
-        <v>0.6529682367991271</v>
+        <v>0.6606924154297669</v>
       </c>
       <c r="U5">
-        <v>0.09</v>
+        <v>0.2008</v>
       </c>
       <c r="V5">
-        <v>0.15</v>
+        <v>0.07770472053957242</v>
       </c>
       <c r="W5">
-        <v>0.0765</v>
+        <v>0.1851968921156538</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y5">
-        <v>1.541047692281101</v>
+        <v>0.5180314702638161</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1000406170452528</v>
+        <v>0.1033631385823995</v>
       </c>
       <c r="C6">
-        <v>490.9022078033032</v>
+        <v>470.144452912747</v>
       </c>
       <c r="D6">
-        <v>505.6182078033031</v>
+        <v>490.094452912747</v>
       </c>
       <c r="E6">
-        <v>-113.564</v>
+        <v>-108.33</v>
       </c>
       <c r="F6">
-        <v>20.936</v>
+        <v>26.17</v>
       </c>
       <c r="G6">
         <v>6.22</v>
@@ -1779,45 +1779,45 @@
         <v>2.177777777777806</v>
       </c>
       <c r="M6">
-        <v>4.2039488</v>
+        <v>6.170886</v>
       </c>
       <c r="N6">
-        <v>-2.026171022222194</v>
+        <v>-3.993108222222195</v>
       </c>
       <c r="O6">
-        <v>-0.3039256533333292</v>
+        <v>-0.5989662333333292</v>
       </c>
       <c r="P6">
-        <v>-1.722245368888865</v>
+        <v>-3.394141988888865</v>
       </c>
       <c r="Q6">
-        <v>170.8777546311111</v>
+        <v>169.2058580111111</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.09649243891731946</v>
+        <v>0.09704975041870878</v>
       </c>
       <c r="T6">
-        <v>0.6606924154297669</v>
+        <v>0.6679560525690308</v>
       </c>
       <c r="U6">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V6">
-        <v>0.07770472053957242</v>
+        <v>0.05293675278828208</v>
       </c>
       <c r="W6">
-        <v>0.1851968921156538</v>
+        <v>0.2233175136925231</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y6">
-        <v>0.5180314702638161</v>
+        <v>0.3529116852552139</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1033631385823995</v>
+        <v>0.1052631385823995</v>
       </c>
       <c r="C7">
-        <v>470.144452912747</v>
+        <v>456.4541458609127</v>
       </c>
       <c r="D7">
-        <v>490.094452912747</v>
+        <v>481.6381458609126</v>
       </c>
       <c r="E7">
-        <v>-108.33</v>
+        <v>-103.096</v>
       </c>
       <c r="F7">
-        <v>26.17</v>
+        <v>31.404</v>
       </c>
       <c r="G7">
         <v>6.22</v>
@@ -1861,37 +1861,37 @@
         <v>2.177777777777806</v>
       </c>
       <c r="M7">
-        <v>6.170886</v>
+        <v>7.4050632</v>
       </c>
       <c r="N7">
-        <v>-3.993108222222195</v>
+        <v>-5.227285422222194</v>
       </c>
       <c r="O7">
-        <v>-0.5989662333333292</v>
+        <v>-0.7840928133333291</v>
       </c>
       <c r="P7">
-        <v>-3.394141988888865</v>
+        <v>-4.443192608888865</v>
       </c>
       <c r="Q7">
-        <v>169.2058580111111</v>
+        <v>168.1568073911111</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.09704975041870878</v>
+        <v>0.09759496052954611</v>
       </c>
       <c r="T7">
-        <v>0.6679560525690308</v>
+        <v>0.6750619680218928</v>
       </c>
       <c r="U7">
         <v>0.2358</v>
       </c>
       <c r="V7">
-        <v>0.05293675278828208</v>
+        <v>0.04411396065690174</v>
       </c>
       <c r="W7">
-        <v>0.2233175136925231</v>
+        <v>0.2253979280771026</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>0.3529116852552139</v>
+        <v>0.2940930710460116</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1052631385823995</v>
+        <v>0.1071631385823995</v>
       </c>
       <c r="C8">
-        <v>456.4541458609127</v>
+        <v>443.0507068060702</v>
       </c>
       <c r="D8">
-        <v>481.6381458609126</v>
+        <v>473.4687068060701</v>
       </c>
       <c r="E8">
-        <v>-103.096</v>
+        <v>-97.86199999999999</v>
       </c>
       <c r="F8">
-        <v>31.404</v>
+        <v>36.638</v>
       </c>
       <c r="G8">
         <v>6.22</v>
@@ -1943,37 +1943,37 @@
         <v>2.177777777777806</v>
       </c>
       <c r="M8">
-        <v>7.4050632</v>
+        <v>8.6392404</v>
       </c>
       <c r="N8">
-        <v>-5.227285422222194</v>
+        <v>-6.461462622222195</v>
       </c>
       <c r="O8">
-        <v>-0.7840928133333291</v>
+        <v>-0.9692193933333292</v>
       </c>
       <c r="P8">
-        <v>-4.443192608888865</v>
+        <v>-5.492243228888865</v>
       </c>
       <c r="Q8">
-        <v>168.1568073911111</v>
+        <v>167.1077567711111</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.09759496052954611</v>
+        <v>0.0981518955890036</v>
       </c>
       <c r="T8">
-        <v>0.6750619680218928</v>
+        <v>0.6823206988608379</v>
       </c>
       <c r="U8">
         <v>0.2358</v>
       </c>
       <c r="V8">
-        <v>0.04411396065690174</v>
+        <v>0.03781196627734434</v>
       </c>
       <c r="W8">
-        <v>0.2253979280771026</v>
+        <v>0.2268839383518022</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>0.2940930710460116</v>
+        <v>0.2520797751822956</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1071631385823995</v>
+        <v>0.1090631385823995</v>
       </c>
       <c r="C9">
-        <v>443.0507068060701</v>
+        <v>429.9197818425816</v>
       </c>
       <c r="D9">
-        <v>473.4687068060701</v>
+        <v>465.5717818425816</v>
       </c>
       <c r="E9">
-        <v>-97.86199999999999</v>
+        <v>-92.628</v>
       </c>
       <c r="F9">
-        <v>36.63800000000001</v>
+        <v>41.872</v>
       </c>
       <c r="G9">
         <v>6.22</v>
@@ -2025,37 +2025,37 @@
         <v>2.177777777777806</v>
       </c>
       <c r="M9">
-        <v>8.639240400000002</v>
+        <v>9.8734176</v>
       </c>
       <c r="N9">
-        <v>-6.461462622222196</v>
+        <v>-7.695639822222194</v>
       </c>
       <c r="O9">
-        <v>-0.9692193933333294</v>
+        <v>-1.154345973333329</v>
       </c>
       <c r="P9">
-        <v>-5.492243228888867</v>
+        <v>-6.541293848888865</v>
       </c>
       <c r="Q9">
-        <v>167.1077567711111</v>
+        <v>166.0587061511111</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.0981518955890036</v>
+        <v>0.09872093793236233</v>
       </c>
       <c r="T9">
-        <v>0.6823206988608379</v>
+        <v>0.6897372281962818</v>
       </c>
       <c r="U9">
         <v>0.2358</v>
       </c>
       <c r="V9">
-        <v>0.03781196627734434</v>
+        <v>0.03308547049267629</v>
       </c>
       <c r="W9">
-        <v>0.2268839383518022</v>
+        <v>0.2279984460578269</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>0.2520797751822955</v>
+        <v>0.2205698032845087</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1090631385823995</v>
+        <v>0.1109631385823995</v>
       </c>
       <c r="C10">
-        <v>429.9197818425816</v>
+        <v>417.0479589826218</v>
       </c>
       <c r="D10">
-        <v>465.5717818425816</v>
+        <v>457.9339589826218</v>
       </c>
       <c r="E10">
-        <v>-92.628</v>
+        <v>-87.39400000000001</v>
       </c>
       <c r="F10">
-        <v>41.872</v>
+        <v>47.10599999999999</v>
       </c>
       <c r="G10">
         <v>6.22</v>
@@ -2107,37 +2107,37 @@
         <v>2.177777777777806</v>
       </c>
       <c r="M10">
-        <v>9.8734176</v>
+        <v>11.1075948</v>
       </c>
       <c r="N10">
-        <v>-7.695639822222194</v>
+        <v>-8.929817022222194</v>
       </c>
       <c r="O10">
-        <v>-1.154345973333329</v>
+        <v>-1.339472553333329</v>
       </c>
       <c r="P10">
-        <v>-6.541293848888865</v>
+        <v>-7.590344468888865</v>
       </c>
       <c r="Q10">
-        <v>166.0587061511111</v>
+        <v>165.0096555311111</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.09872093793236233</v>
+        <v>0.09930248670084983</v>
       </c>
       <c r="T10">
-        <v>0.6897372281962818</v>
+        <v>0.6973167581764607</v>
       </c>
       <c r="U10">
         <v>0.2358</v>
       </c>
       <c r="V10">
-        <v>0.03308547049267629</v>
+        <v>0.02940930710460115</v>
       </c>
       <c r="W10">
-        <v>0.2279984460578269</v>
+        <v>0.2288652853847351</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>0.2205698032845087</v>
+        <v>0.1960620473640077</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1109631385823995</v>
+        <v>0.1128631385823995</v>
       </c>
       <c r="C11">
-        <v>417.0479589826218</v>
+        <v>404.422692141223</v>
       </c>
       <c r="D11">
-        <v>457.9339589826218</v>
+        <v>450.542692141223</v>
       </c>
       <c r="E11">
-        <v>-87.39400000000001</v>
+        <v>-82.16</v>
       </c>
       <c r="F11">
-        <v>47.10599999999999</v>
+        <v>52.34</v>
       </c>
       <c r="G11">
         <v>6.22</v>
@@ -2189,37 +2189,37 @@
         <v>2.177777777777806</v>
       </c>
       <c r="M11">
-        <v>11.1075948</v>
+        <v>12.341772</v>
       </c>
       <c r="N11">
-        <v>-8.929817022222194</v>
+        <v>-10.16399422222219</v>
       </c>
       <c r="O11">
-        <v>-1.339472553333329</v>
+        <v>-1.524599133333329</v>
       </c>
       <c r="P11">
-        <v>-7.590344468888865</v>
+        <v>-8.639395088888865</v>
       </c>
       <c r="Q11">
-        <v>165.0096555311111</v>
+        <v>163.9606049111111</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.09930248670084983</v>
+        <v>0.09989695877530372</v>
       </c>
       <c r="T11">
-        <v>0.6973167581764607</v>
+        <v>0.7050647221561991</v>
       </c>
       <c r="U11">
         <v>0.2358</v>
       </c>
       <c r="V11">
-        <v>0.02940930710460115</v>
+        <v>0.02646837639414104</v>
       </c>
       <c r="W11">
-        <v>0.2288652853847351</v>
+        <v>0.2295587568462616</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>0.1960620473640077</v>
+        <v>0.1764558426276069</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1128631385823995</v>
+        <v>0.1147631385823995</v>
       </c>
       <c r="C12">
-        <v>404.4226921412229</v>
+        <v>392.0322323658885</v>
       </c>
       <c r="D12">
-        <v>450.5426921412229</v>
+        <v>443.3862323658885</v>
       </c>
       <c r="E12">
-        <v>-82.16</v>
+        <v>-76.926</v>
       </c>
       <c r="F12">
-        <v>52.34</v>
+        <v>57.574</v>
       </c>
       <c r="G12">
         <v>6.22</v>
@@ -2271,37 +2271,37 @@
         <v>2.177777777777806</v>
       </c>
       <c r="M12">
-        <v>12.341772</v>
+        <v>13.5759492</v>
       </c>
       <c r="N12">
-        <v>-10.1639942222222</v>
+        <v>-11.39817142222219</v>
       </c>
       <c r="O12">
-        <v>-1.524599133333329</v>
+        <v>-1.709725713333329</v>
       </c>
       <c r="P12">
-        <v>-8.639395088888866</v>
+        <v>-9.688445708888866</v>
       </c>
       <c r="Q12">
-        <v>163.9606049111111</v>
+        <v>162.9115542911111</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.09989695877530372</v>
+        <v>0.100504789772779</v>
       </c>
       <c r="T12">
-        <v>0.7050647221561991</v>
+        <v>0.7129867976860441</v>
       </c>
       <c r="U12">
         <v>0.2358</v>
       </c>
       <c r="V12">
-        <v>0.02646837639414104</v>
+        <v>0.02406216035831003</v>
       </c>
       <c r="W12">
-        <v>0.2295587568462616</v>
+        <v>0.2301261425875105</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>0.1764558426276069</v>
+        <v>0.1604144023887336</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1147631385823995</v>
+        <v>0.1166631385823995</v>
       </c>
       <c r="C13">
-        <v>392.0322323658885</v>
+        <v>379.865565517858</v>
       </c>
       <c r="D13">
-        <v>443.3862323658885</v>
+        <v>436.453565517858</v>
       </c>
       <c r="E13">
-        <v>-76.926</v>
+        <v>-71.69200000000001</v>
       </c>
       <c r="F13">
-        <v>57.574</v>
+        <v>62.80799999999999</v>
       </c>
       <c r="G13">
         <v>6.22</v>
@@ -2353,37 +2353,37 @@
         <v>2.177777777777806</v>
       </c>
       <c r="M13">
-        <v>13.5759492</v>
+        <v>14.8101264</v>
       </c>
       <c r="N13">
-        <v>-11.39817142222219</v>
+        <v>-12.63234862222219</v>
       </c>
       <c r="O13">
-        <v>-1.709725713333329</v>
+        <v>-1.894852293333329</v>
       </c>
       <c r="P13">
-        <v>-9.688445708888866</v>
+        <v>-10.73749632888886</v>
       </c>
       <c r="Q13">
-        <v>162.9115542911111</v>
+        <v>161.8625036711111</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.100504789772779</v>
+        <v>0.1011264351111061</v>
       </c>
       <c r="T13">
-        <v>0.7129867976860441</v>
+        <v>0.7210889203870219</v>
       </c>
       <c r="U13">
         <v>0.2358</v>
       </c>
       <c r="V13">
-        <v>0.02406216035831003</v>
+        <v>0.02205698032845087</v>
       </c>
       <c r="W13">
-        <v>0.2301261425875105</v>
+        <v>0.2305989640385513</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>0.1604144023887336</v>
+        <v>0.1470465355230057</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1166631385823995</v>
+        <v>0.1185631385823995</v>
       </c>
       <c r="C14">
-        <v>379.865565517858</v>
+        <v>367.9123557097595</v>
       </c>
       <c r="D14">
-        <v>436.453565517858</v>
+        <v>429.7343557097595</v>
       </c>
       <c r="E14">
-        <v>-71.69200000000001</v>
+        <v>-66.458</v>
       </c>
       <c r="F14">
-        <v>62.80799999999999</v>
+        <v>68.042</v>
       </c>
       <c r="G14">
         <v>6.22</v>
@@ -2435,37 +2435,37 @@
         <v>2.177777777777806</v>
       </c>
       <c r="M14">
-        <v>14.8101264</v>
+        <v>16.0443036</v>
       </c>
       <c r="N14">
-        <v>-12.63234862222219</v>
+        <v>-13.8665258222222</v>
       </c>
       <c r="O14">
-        <v>-1.894852293333329</v>
+        <v>-2.079978873333329</v>
       </c>
       <c r="P14">
-        <v>-10.73749632888886</v>
+        <v>-11.78654694888887</v>
       </c>
       <c r="Q14">
-        <v>161.8625036711111</v>
+        <v>160.8134530511111</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1011264351111061</v>
+        <v>0.1017623711468659</v>
       </c>
       <c r="T14">
-        <v>0.7210889203870219</v>
+        <v>0.7293772987822751</v>
       </c>
       <c r="U14">
         <v>0.2358</v>
       </c>
       <c r="V14">
-        <v>0.02205698032845087</v>
+        <v>0.02036028953395464</v>
       </c>
       <c r="W14">
-        <v>0.2305989640385513</v>
+        <v>0.2309990437278935</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>0.1470465355230057</v>
+        <v>0.1357352635596976</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1185631385823995</v>
+        <v>0.1204631385823995</v>
       </c>
       <c r="C15">
-        <v>367.9123557097595</v>
+        <v>356.1628938887166</v>
       </c>
       <c r="D15">
-        <v>429.7343557097595</v>
+        <v>423.2188938887165</v>
       </c>
       <c r="E15">
-        <v>-66.458</v>
+        <v>-61.22399999999999</v>
       </c>
       <c r="F15">
-        <v>68.042</v>
+        <v>73.27600000000001</v>
       </c>
       <c r="G15">
         <v>6.22</v>
@@ -2517,37 +2517,37 @@
         <v>2.177777777777806</v>
       </c>
       <c r="M15">
-        <v>16.0443036</v>
+        <v>17.2784808</v>
       </c>
       <c r="N15">
-        <v>-13.8665258222222</v>
+        <v>-15.1007030222222</v>
       </c>
       <c r="O15">
-        <v>-2.079978873333329</v>
+        <v>-2.26510545333333</v>
       </c>
       <c r="P15">
-        <v>-11.78654694888887</v>
+        <v>-12.83559756888887</v>
       </c>
       <c r="Q15">
-        <v>160.8134530511111</v>
+        <v>159.7644024311111</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1017623711468659</v>
+        <v>0.1024130963927597</v>
       </c>
       <c r="T15">
-        <v>0.7293772987822751</v>
+        <v>0.7378584301634642</v>
       </c>
       <c r="U15">
         <v>0.2358</v>
       </c>
       <c r="V15">
-        <v>0.02036028953395464</v>
+        <v>0.01890598313867217</v>
       </c>
       <c r="W15">
-        <v>0.2309990437278935</v>
+        <v>0.2313419691759011</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>0.1357352635596976</v>
+        <v>0.1260398875911478</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1204631385823995</v>
+        <v>0.1223631385823995</v>
       </c>
       <c r="C16">
-        <v>356.1628938887166</v>
+        <v>344.6080510269741</v>
       </c>
       <c r="D16">
-        <v>423.2188938887165</v>
+        <v>416.8980510269741</v>
       </c>
       <c r="E16">
-        <v>-61.22399999999999</v>
+        <v>-55.98999999999999</v>
       </c>
       <c r="F16">
-        <v>73.27600000000001</v>
+        <v>78.51000000000001</v>
       </c>
       <c r="G16">
         <v>6.22</v>
@@ -2599,37 +2599,37 @@
         <v>2.177777777777806</v>
       </c>
       <c r="M16">
-        <v>17.2784808</v>
+        <v>18.512658</v>
       </c>
       <c r="N16">
-        <v>-15.1007030222222</v>
+        <v>-16.3348802222222</v>
       </c>
       <c r="O16">
-        <v>-2.26510545333333</v>
+        <v>-2.450232033333329</v>
       </c>
       <c r="P16">
-        <v>-12.83559756888887</v>
+        <v>-13.88464818888887</v>
       </c>
       <c r="Q16">
-        <v>159.7644024311111</v>
+        <v>158.7153518111111</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1024130963927597</v>
+        <v>0.1030791328209098</v>
       </c>
       <c r="T16">
-        <v>0.7378584301634642</v>
+        <v>0.7465391175771521</v>
       </c>
       <c r="U16">
         <v>0.2358</v>
       </c>
       <c r="V16">
-        <v>0.01890598313867217</v>
+        <v>0.01764558426276069</v>
       </c>
       <c r="W16">
-        <v>0.2313419691759011</v>
+        <v>0.231639171230841</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>0.1260398875911478</v>
+        <v>0.1176372284184046</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1223631385823995</v>
+        <v>0.1242631385823995</v>
       </c>
       <c r="C17">
-        <v>344.6080510269742</v>
+        <v>333.2392354454321</v>
       </c>
       <c r="D17">
-        <v>416.8980510269741</v>
+        <v>410.7632354454321</v>
       </c>
       <c r="E17">
-        <v>-55.99000000000001</v>
+        <v>-50.756</v>
       </c>
       <c r="F17">
-        <v>78.50999999999999</v>
+        <v>83.744</v>
       </c>
       <c r="G17">
         <v>6.22</v>
@@ -2681,37 +2681,37 @@
         <v>2.177777777777806</v>
       </c>
       <c r="M17">
-        <v>18.512658</v>
+        <v>19.7468352</v>
       </c>
       <c r="N17">
-        <v>-16.33488022222219</v>
+        <v>-17.56905742222219</v>
       </c>
       <c r="O17">
-        <v>-2.450232033333329</v>
+        <v>-2.635358613333329</v>
       </c>
       <c r="P17">
-        <v>-13.88464818888886</v>
+        <v>-14.93369880888886</v>
       </c>
       <c r="Q17">
-        <v>158.7153518111111</v>
+        <v>157.6663011911111</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1030791328209098</v>
+        <v>0.103761027259254</v>
       </c>
       <c r="T17">
-        <v>0.7465391175771521</v>
+        <v>0.7554264880244991</v>
       </c>
       <c r="U17">
         <v>0.2358</v>
       </c>
       <c r="V17">
-        <v>0.01764558426276069</v>
+        <v>0.01654273524633815</v>
       </c>
       <c r="W17">
-        <v>0.231639171230841</v>
+        <v>0.2318992230289135</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>0.1176372284184046</v>
+        <v>0.1102849016422544</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1242631385823995</v>
+        <v>0.1261631385823995</v>
       </c>
       <c r="C18">
-        <v>333.2392354454321</v>
+        <v>322.0483538505388</v>
       </c>
       <c r="D18">
-        <v>410.7632354454321</v>
+        <v>404.8063538505388</v>
       </c>
       <c r="E18">
-        <v>-50.756</v>
+        <v>-45.52199999999999</v>
       </c>
       <c r="F18">
-        <v>83.744</v>
+        <v>88.97800000000001</v>
       </c>
       <c r="G18">
         <v>6.22</v>
@@ -2763,37 +2763,37 @@
         <v>2.177777777777806</v>
       </c>
       <c r="M18">
-        <v>19.7468352</v>
+        <v>20.9810124</v>
       </c>
       <c r="N18">
-        <v>-17.56905742222219</v>
+        <v>-18.8032346222222</v>
       </c>
       <c r="O18">
-        <v>-2.635358613333329</v>
+        <v>-2.82048519333333</v>
       </c>
       <c r="P18">
-        <v>-14.93369880888886</v>
+        <v>-15.98274942888887</v>
       </c>
       <c r="Q18">
-        <v>157.6663011911111</v>
+        <v>156.6172505711111</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.103761027259254</v>
+        <v>0.1044593528888836</v>
       </c>
       <c r="T18">
-        <v>0.7554264880244991</v>
+        <v>0.7645280119766015</v>
       </c>
       <c r="U18">
         <v>0.2358</v>
       </c>
       <c r="V18">
-        <v>0.01654273524633815</v>
+        <v>0.01556963317302414</v>
       </c>
       <c r="W18">
-        <v>0.2318992230289135</v>
+        <v>0.2321286804978009</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>0.1102849016422544</v>
+        <v>0.1037975544868276</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1261631385823995</v>
+        <v>0.1280631385823995</v>
       </c>
       <c r="C19">
-        <v>322.0483538505388</v>
+        <v>311.0277757129761</v>
       </c>
       <c r="D19">
-        <v>404.8063538505388</v>
+        <v>399.019775712976</v>
       </c>
       <c r="E19">
-        <v>-45.52199999999999</v>
+        <v>-40.288</v>
       </c>
       <c r="F19">
-        <v>88.97800000000001</v>
+        <v>94.212</v>
       </c>
       <c r="G19">
         <v>6.22</v>
@@ -2845,37 +2845,37 @@
         <v>2.177777777777806</v>
       </c>
       <c r="M19">
-        <v>20.9810124</v>
+        <v>22.2151896</v>
       </c>
       <c r="N19">
-        <v>-18.8032346222222</v>
+        <v>-20.0374118222222</v>
       </c>
       <c r="O19">
-        <v>-2.82048519333333</v>
+        <v>-3.005611773333329</v>
       </c>
       <c r="P19">
-        <v>-15.98274942888887</v>
+        <v>-17.03180004888887</v>
       </c>
       <c r="Q19">
-        <v>156.6172505711111</v>
+        <v>155.5681999511111</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1044593528888836</v>
+        <v>0.1051747108509431</v>
       </c>
       <c r="T19">
-        <v>0.7645280119766015</v>
+        <v>0.7738515243177796</v>
       </c>
       <c r="U19">
         <v>0.2358</v>
       </c>
       <c r="V19">
-        <v>0.01556963317302414</v>
+        <v>0.01470465355230057</v>
       </c>
       <c r="W19">
-        <v>0.2321286804978009</v>
+        <v>0.2323326426923675</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>0.1037975544868276</v>
+        <v>0.09803102368200389</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1280631385823995</v>
+        <v>0.1299631385823995</v>
       </c>
       <c r="C20">
-        <v>311.0277757129761</v>
+        <v>300.1703006584594</v>
       </c>
       <c r="D20">
-        <v>399.019775712976</v>
+        <v>393.3963006584593</v>
       </c>
       <c r="E20">
-        <v>-40.28800000000001</v>
+        <v>-35.054</v>
       </c>
       <c r="F20">
-        <v>94.21199999999999</v>
+        <v>99.446</v>
       </c>
       <c r="G20">
         <v>6.22</v>
@@ -2927,37 +2927,37 @@
         <v>2.177777777777806</v>
       </c>
       <c r="M20">
-        <v>22.2151896</v>
+        <v>23.4493668</v>
       </c>
       <c r="N20">
-        <v>-20.03741182222219</v>
+        <v>-21.27158902222219</v>
       </c>
       <c r="O20">
-        <v>-3.005611773333329</v>
+        <v>-3.190738353333329</v>
       </c>
       <c r="P20">
-        <v>-17.03180004888887</v>
+        <v>-18.08085066888886</v>
       </c>
       <c r="Q20">
-        <v>155.5681999511111</v>
+        <v>154.5191493311111</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1051747108509431</v>
+        <v>0.1059077319725597</v>
       </c>
       <c r="T20">
-        <v>0.7738515243177795</v>
+        <v>0.7834052468402213</v>
       </c>
       <c r="U20">
         <v>0.2358</v>
       </c>
       <c r="V20">
-        <v>0.01470465355230058</v>
+        <v>0.01393072441796897</v>
       </c>
       <c r="W20">
-        <v>0.2323326426923675</v>
+        <v>0.2325151351822429</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>0.09803102368200389</v>
+        <v>0.09287149611979317</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1299631385823995</v>
+        <v>0.1318631385823995</v>
       </c>
       <c r="C21">
-        <v>300.1703006584594</v>
+        <v>289.4691285776303</v>
       </c>
       <c r="D21">
-        <v>393.3963006584593</v>
+        <v>387.9291285776303</v>
       </c>
       <c r="E21">
-        <v>-35.054</v>
+        <v>-29.81999999999999</v>
       </c>
       <c r="F21">
-        <v>99.446</v>
+        <v>104.68</v>
       </c>
       <c r="G21">
         <v>6.22</v>
@@ -3009,37 +3009,37 @@
         <v>2.177777777777806</v>
       </c>
       <c r="M21">
-        <v>23.4493668</v>
+        <v>24.683544</v>
       </c>
       <c r="N21">
-        <v>-21.27158902222219</v>
+        <v>-22.5057662222222</v>
       </c>
       <c r="O21">
-        <v>-3.190738353333329</v>
+        <v>-3.375864933333329</v>
       </c>
       <c r="P21">
-        <v>-18.08085066888886</v>
+        <v>-19.12990128888887</v>
       </c>
       <c r="Q21">
-        <v>154.5191493311111</v>
+        <v>153.4700987111111</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1059077319725597</v>
+        <v>0.1066590786222167</v>
       </c>
       <c r="T21">
-        <v>0.7834052468402213</v>
+        <v>0.793197812425724</v>
       </c>
       <c r="U21">
         <v>0.2358</v>
       </c>
       <c r="V21">
-        <v>0.01393072441796897</v>
+        <v>0.01323418819707052</v>
       </c>
       <c r="W21">
-        <v>0.2325151351822429</v>
+        <v>0.2326793784231308</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>0.09287149611979317</v>
+        <v>0.08822792131380341</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1318631385823995</v>
+        <v>0.1337631385823995</v>
       </c>
       <c r="C22">
-        <v>289.4691285776303</v>
+        <v>278.9178321941476</v>
       </c>
       <c r="D22">
-        <v>387.9291285776303</v>
+        <v>382.6118321941476</v>
       </c>
       <c r="E22">
-        <v>-29.81999999999999</v>
+        <v>-24.586</v>
       </c>
       <c r="F22">
-        <v>104.68</v>
+        <v>109.914</v>
       </c>
       <c r="G22">
         <v>6.22</v>
@@ -3091,37 +3091,37 @@
         <v>2.177777777777806</v>
       </c>
       <c r="M22">
-        <v>24.683544</v>
+        <v>25.9177212</v>
       </c>
       <c r="N22">
-        <v>-22.5057662222222</v>
+        <v>-23.7399434222222</v>
       </c>
       <c r="O22">
-        <v>-3.375864933333329</v>
+        <v>-3.56099151333333</v>
       </c>
       <c r="P22">
-        <v>-19.12990128888887</v>
+        <v>-20.17895190888887</v>
       </c>
       <c r="Q22">
-        <v>153.4700987111111</v>
+        <v>152.4210480911111</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1066590786222167</v>
+        <v>0.1074294467060422</v>
       </c>
       <c r="T22">
-        <v>0.793197812425724</v>
+        <v>0.8032382910640243</v>
       </c>
       <c r="U22">
         <v>0.2358</v>
       </c>
       <c r="V22">
-        <v>0.01323418819707052</v>
+        <v>0.01260398875911478</v>
       </c>
       <c r="W22">
-        <v>0.2326793784231308</v>
+        <v>0.2328279794506008</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>0.08822792131380341</v>
+        <v>0.08402659172743188</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1337631385823995</v>
+        <v>0.1356631385823995</v>
       </c>
       <c r="C23">
-        <v>278.9178321941477</v>
+        <v>268.5103318583091</v>
       </c>
       <c r="D23">
-        <v>382.6118321941477</v>
+        <v>377.4383318583091</v>
       </c>
       <c r="E23">
-        <v>-24.58600000000001</v>
+        <v>-19.352</v>
       </c>
       <c r="F23">
-        <v>109.914</v>
+        <v>115.148</v>
       </c>
       <c r="G23">
         <v>6.22</v>
@@ -3173,37 +3173,37 @@
         <v>2.177777777777806</v>
       </c>
       <c r="M23">
-        <v>25.9177212</v>
+        <v>27.1518984</v>
       </c>
       <c r="N23">
-        <v>-23.73994342222219</v>
+        <v>-24.97412062222219</v>
       </c>
       <c r="O23">
-        <v>-3.560991513333329</v>
+        <v>-3.746118093333329</v>
       </c>
       <c r="P23">
-        <v>-20.17895190888887</v>
+        <v>-21.22800252888887</v>
       </c>
       <c r="Q23">
-        <v>152.4210480911111</v>
+        <v>151.3719974711111</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1074294467060422</v>
+        <v>0.1082195678176581</v>
       </c>
       <c r="T23">
-        <v>0.8032382910640243</v>
+        <v>0.8135362178725375</v>
       </c>
       <c r="U23">
         <v>0.2358</v>
       </c>
       <c r="V23">
-        <v>0.01260398875911478</v>
+        <v>0.01203108017915502</v>
       </c>
       <c r="W23">
-        <v>0.2328279794506008</v>
+        <v>0.2329630712937553</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>0.08402659172743188</v>
+        <v>0.08020720119436675</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1356631385823995</v>
+        <v>0.1375631385823995</v>
       </c>
       <c r="C24">
-        <v>268.5103318583091</v>
+        <v>258.2408723583644</v>
       </c>
       <c r="D24">
-        <v>377.4383318583091</v>
+        <v>372.4028723583644</v>
       </c>
       <c r="E24">
-        <v>-19.352</v>
+        <v>-14.11799999999999</v>
       </c>
       <c r="F24">
-        <v>115.148</v>
+        <v>120.382</v>
       </c>
       <c r="G24">
         <v>6.22</v>
@@ -3255,37 +3255,37 @@
         <v>2.177777777777806</v>
       </c>
       <c r="M24">
-        <v>27.1518984</v>
+        <v>28.3860756</v>
       </c>
       <c r="N24">
-        <v>-24.97412062222219</v>
+        <v>-26.2082978222222</v>
       </c>
       <c r="O24">
-        <v>-3.746118093333329</v>
+        <v>-3.931244673333329</v>
       </c>
       <c r="P24">
-        <v>-21.22800252888887</v>
+        <v>-22.27705314888887</v>
       </c>
       <c r="Q24">
-        <v>151.3719974711111</v>
+        <v>150.3229468511111</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1082195678176581</v>
+        <v>0.1090302115555498</v>
       </c>
       <c r="T24">
-        <v>0.8135362178725375</v>
+        <v>0.8241016232994536</v>
       </c>
       <c r="U24">
         <v>0.2358</v>
       </c>
       <c r="V24">
-        <v>0.01203108017915502</v>
+        <v>0.01150798973658306</v>
       </c>
       <c r="W24">
-        <v>0.2329630712937553</v>
+        <v>0.2330864160201137</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>0.08020720119436675</v>
+        <v>0.07671993157722035</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1375631385823995</v>
+        <v>0.1394631385823995</v>
       </c>
       <c r="C25">
-        <v>258.2408723583644</v>
+        <v>248.1040015635729</v>
       </c>
       <c r="D25">
-        <v>372.4028723583644</v>
+        <v>367.5000015635728</v>
       </c>
       <c r="E25">
-        <v>-14.11799999999999</v>
+        <v>-8.884</v>
       </c>
       <c r="F25">
-        <v>120.382</v>
+        <v>125.616</v>
       </c>
       <c r="G25">
         <v>6.22</v>
@@ -3337,37 +3337,37 @@
         <v>2.177777777777806</v>
       </c>
       <c r="M25">
-        <v>28.3860756</v>
+        <v>29.6202528</v>
       </c>
       <c r="N25">
-        <v>-26.2082978222222</v>
+        <v>-27.44247502222219</v>
       </c>
       <c r="O25">
-        <v>-3.931244673333329</v>
+        <v>-4.116371253333329</v>
       </c>
       <c r="P25">
-        <v>-22.27705314888887</v>
+        <v>-23.32610376888886</v>
       </c>
       <c r="Q25">
-        <v>150.3229468511111</v>
+        <v>149.2738962311111</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1090302115555498</v>
+        <v>0.109862188023386</v>
       </c>
       <c r="T25">
-        <v>0.8241016232994536</v>
+        <v>0.8349450657112885</v>
       </c>
       <c r="U25">
         <v>0.2358</v>
       </c>
       <c r="V25">
-        <v>0.01150798973658306</v>
+        <v>0.01102849016422543</v>
       </c>
       <c r="W25">
-        <v>0.2330864160201137</v>
+        <v>0.2331994820192757</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>0.07671993157722035</v>
+        <v>0.07352326776150286</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1394631385823995</v>
+        <v>0.1413631385823995</v>
       </c>
       <c r="C26">
-        <v>248.1040015635729</v>
+        <v>238.094550732387</v>
       </c>
       <c r="D26">
-        <v>367.5000015635728</v>
+        <v>362.724550732387</v>
       </c>
       <c r="E26">
-        <v>-8.884000000000015</v>
+        <v>-3.650000000000006</v>
       </c>
       <c r="F26">
-        <v>125.616</v>
+        <v>130.85</v>
       </c>
       <c r="G26">
         <v>6.22</v>
@@ -3419,37 +3419,37 @@
         <v>2.177777777777806</v>
       </c>
       <c r="M26">
-        <v>29.6202528</v>
+        <v>30.85443</v>
       </c>
       <c r="N26">
-        <v>-27.44247502222219</v>
+        <v>-28.6766522222222</v>
       </c>
       <c r="O26">
-        <v>-4.116371253333329</v>
+        <v>-4.301497833333329</v>
       </c>
       <c r="P26">
-        <v>-23.32610376888886</v>
+        <v>-24.37515438888887</v>
       </c>
       <c r="Q26">
-        <v>149.2738962311111</v>
+        <v>148.2248456111111</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.109862188023386</v>
+        <v>0.1107163505303645</v>
       </c>
       <c r="T26">
-        <v>0.8349450657112885</v>
+        <v>0.8460776665874389</v>
       </c>
       <c r="U26">
         <v>0.2358</v>
       </c>
       <c r="V26">
-        <v>0.01102849016422543</v>
+        <v>0.01058735055765641</v>
       </c>
       <c r="W26">
-        <v>0.2331994820192757</v>
+        <v>0.2333035027385046</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>0.07352326776150286</v>
+        <v>0.07058233705104278</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1413631385823995</v>
+        <v>0.1432631385823995</v>
       </c>
       <c r="C27">
-        <v>238.094550732387</v>
+        <v>228.2076163362462</v>
       </c>
       <c r="D27">
-        <v>362.724550732387</v>
+        <v>358.0716163362462</v>
       </c>
       <c r="E27">
-        <v>-3.650000000000006</v>
+        <v>1.584000000000003</v>
       </c>
       <c r="F27">
-        <v>130.85</v>
+        <v>136.084</v>
       </c>
       <c r="G27">
         <v>6.22</v>
@@ -3501,37 +3501,37 @@
         <v>2.177777777777806</v>
       </c>
       <c r="M27">
-        <v>30.85443</v>
+        <v>32.08860720000001</v>
       </c>
       <c r="N27">
-        <v>-28.6766522222222</v>
+        <v>-29.9108294222222</v>
       </c>
       <c r="O27">
-        <v>-4.301497833333329</v>
+        <v>-4.48662441333333</v>
       </c>
       <c r="P27">
-        <v>-24.37515438888887</v>
+        <v>-25.42420500888887</v>
       </c>
       <c r="Q27">
-        <v>148.2248456111111</v>
+        <v>147.1757949911111</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1107163505303645</v>
+        <v>0.1115935985105045</v>
       </c>
       <c r="T27">
-        <v>0.8460776665874389</v>
+        <v>0.8575111485683503</v>
       </c>
       <c r="U27">
         <v>0.2358</v>
       </c>
       <c r="V27">
-        <v>0.01058735055765641</v>
+        <v>0.01018014476697732</v>
       </c>
       <c r="W27">
-        <v>0.2333035027385046</v>
+        <v>0.2333995218639467</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>0.07058233705104278</v>
+        <v>0.06786763177984878</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1432631385823995</v>
+        <v>0.1451631385823995</v>
       </c>
       <c r="C28">
-        <v>228.2076163362462</v>
+        <v>218.4385432646077</v>
       </c>
       <c r="D28">
-        <v>358.0716163362462</v>
+        <v>353.5365432646077</v>
       </c>
       <c r="E28">
-        <v>1.584000000000003</v>
+        <v>6.818000000000012</v>
       </c>
       <c r="F28">
-        <v>136.084</v>
+        <v>141.318</v>
       </c>
       <c r="G28">
         <v>6.22</v>
@@ -3583,37 +3583,37 @@
         <v>2.177777777777806</v>
       </c>
       <c r="M28">
-        <v>32.08860720000001</v>
+        <v>33.3227844</v>
       </c>
       <c r="N28">
-        <v>-29.9108294222222</v>
+        <v>-31.1450066222222</v>
       </c>
       <c r="O28">
-        <v>-4.48662441333333</v>
+        <v>-4.67175099333333</v>
       </c>
       <c r="P28">
-        <v>-25.42420500888887</v>
+        <v>-26.47325562888887</v>
       </c>
       <c r="Q28">
-        <v>147.1757949911111</v>
+        <v>146.1267443711111</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1115935985105045</v>
+        <v>0.1124948806818813</v>
       </c>
       <c r="T28">
-        <v>0.8575111485683503</v>
+        <v>0.8692578766309305</v>
       </c>
       <c r="U28">
         <v>0.2358</v>
       </c>
       <c r="V28">
-        <v>0.01018014476697732</v>
+        <v>0.009803102368200383</v>
       </c>
       <c r="W28">
-        <v>0.2333995218639467</v>
+        <v>0.2334884284615784</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>0.06786763177984878</v>
+        <v>0.0653540157880026</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1451631385823995</v>
+        <v>0.1470631385823995</v>
       </c>
       <c r="C29">
-        <v>218.4385432646077</v>
+        <v>208.7829092902935</v>
       </c>
       <c r="D29">
-        <v>353.5365432646077</v>
+        <v>349.1149092902935</v>
       </c>
       <c r="E29">
-        <v>6.818000000000012</v>
+        <v>12.05200000000002</v>
       </c>
       <c r="F29">
-        <v>141.318</v>
+        <v>146.552</v>
       </c>
       <c r="G29">
         <v>6.22</v>
@@ -3665,37 +3665,37 @@
         <v>2.177777777777806</v>
       </c>
       <c r="M29">
-        <v>33.3227844</v>
+        <v>34.55696160000001</v>
       </c>
       <c r="N29">
-        <v>-31.1450066222222</v>
+        <v>-32.3791838222222</v>
       </c>
       <c r="O29">
-        <v>-4.67175099333333</v>
+        <v>-4.85687757333333</v>
       </c>
       <c r="P29">
-        <v>-26.47325562888887</v>
+        <v>-27.52230624888887</v>
       </c>
       <c r="Q29">
-        <v>146.1267443711111</v>
+        <v>145.0776937511111</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1124948806818813</v>
+        <v>0.1134211984691297</v>
       </c>
       <c r="T29">
-        <v>0.8692578766309305</v>
+        <v>0.8813309026952489</v>
       </c>
       <c r="U29">
         <v>0.2358</v>
       </c>
       <c r="V29">
-        <v>0.009803102368200383</v>
+        <v>0.009452991569336084</v>
       </c>
       <c r="W29">
-        <v>0.2334884284615784</v>
+        <v>0.2335709845879506</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>0.0653540157880026</v>
+        <v>0.06301994379557385</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1470631385823995</v>
+        <v>0.1489631385823995</v>
       </c>
       <c r="C30">
-        <v>208.7829092902935</v>
+        <v>199.236510686176</v>
       </c>
       <c r="D30">
-        <v>349.1149092902935</v>
+        <v>344.802510686176</v>
       </c>
       <c r="E30">
-        <v>12.05200000000002</v>
+        <v>17.286</v>
       </c>
       <c r="F30">
-        <v>146.552</v>
+        <v>151.786</v>
       </c>
       <c r="G30">
         <v>6.22</v>
@@ -3747,37 +3747,37 @@
         <v>2.177777777777806</v>
       </c>
       <c r="M30">
-        <v>34.55696160000001</v>
+        <v>35.7911388</v>
       </c>
       <c r="N30">
-        <v>-32.3791838222222</v>
+        <v>-33.61336102222219</v>
       </c>
       <c r="O30">
-        <v>-4.85687757333333</v>
+        <v>-5.042004153333329</v>
       </c>
       <c r="P30">
-        <v>-27.52230624888887</v>
+        <v>-28.57135686888886</v>
       </c>
       <c r="Q30">
-        <v>145.0776937511111</v>
+        <v>144.0286431311111</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1134211984691297</v>
+        <v>0.1143736097151737</v>
       </c>
       <c r="T30">
-        <v>0.8813309026952489</v>
+        <v>0.8937440140008158</v>
       </c>
       <c r="U30">
         <v>0.2358</v>
       </c>
       <c r="V30">
-        <v>0.009452991569336084</v>
+        <v>0.009127026342807255</v>
       </c>
       <c r="W30">
-        <v>0.2335709845879506</v>
+        <v>0.2336478471883661</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>0.06301994379557385</v>
+        <v>0.06084684228538173</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1489631385823995</v>
+        <v>0.1508631385823995</v>
       </c>
       <c r="C31">
-        <v>199.236510686176</v>
+        <v>189.7953488948651</v>
       </c>
       <c r="D31">
-        <v>344.802510686176</v>
+        <v>340.595348894865</v>
       </c>
       <c r="E31">
-        <v>17.28599999999997</v>
+        <v>22.51999999999998</v>
       </c>
       <c r="F31">
-        <v>151.786</v>
+        <v>157.02</v>
       </c>
       <c r="G31">
         <v>6.22</v>
@@ -3829,37 +3829,37 @@
         <v>2.177777777777806</v>
       </c>
       <c r="M31">
-        <v>35.79113879999999</v>
+        <v>37.025316</v>
       </c>
       <c r="N31">
-        <v>-33.61336102222219</v>
+        <v>-34.84753822222219</v>
       </c>
       <c r="O31">
-        <v>-5.042004153333328</v>
+        <v>-5.227130733333328</v>
       </c>
       <c r="P31">
-        <v>-28.57135686888886</v>
+        <v>-29.62040748888886</v>
       </c>
       <c r="Q31">
-        <v>144.0286431311111</v>
+        <v>142.9795925111111</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1143736097151737</v>
+        <v>0.1153532327111048</v>
       </c>
       <c r="T31">
-        <v>0.8937440140008158</v>
+        <v>0.9065117856293989</v>
       </c>
       <c r="U31">
         <v>0.2358</v>
       </c>
       <c r="V31">
-        <v>0.009127026342807256</v>
+        <v>0.008822792131380347</v>
       </c>
       <c r="W31">
-        <v>0.2336478471883661</v>
+        <v>0.2337195856154205</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>0.06084684228538173</v>
+        <v>0.05881861420920231</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1508631385823995</v>
+        <v>0.1527631385823995</v>
       </c>
       <c r="C32">
-        <v>189.7953488948651</v>
+        <v>180.4556181625423</v>
       </c>
       <c r="D32">
-        <v>340.595348894865</v>
+        <v>336.4896181625423</v>
       </c>
       <c r="E32">
-        <v>22.51999999999998</v>
+        <v>27.75399999999999</v>
       </c>
       <c r="F32">
-        <v>157.02</v>
+        <v>162.254</v>
       </c>
       <c r="G32">
         <v>6.22</v>
@@ -3911,37 +3911,37 @@
         <v>2.177777777777806</v>
       </c>
       <c r="M32">
-        <v>37.025316</v>
+        <v>38.2594932</v>
       </c>
       <c r="N32">
-        <v>-34.84753822222219</v>
+        <v>-36.0817154222222</v>
       </c>
       <c r="O32">
-        <v>-5.227130733333328</v>
+        <v>-5.412257313333329</v>
       </c>
       <c r="P32">
-        <v>-29.62040748888886</v>
+        <v>-30.66945810888887</v>
       </c>
       <c r="Q32">
-        <v>142.9795925111111</v>
+        <v>141.9305418911111</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1153532327111048</v>
+        <v>0.1163612505764831</v>
       </c>
       <c r="T32">
-        <v>0.9065117856293989</v>
+        <v>0.9196496375950424</v>
       </c>
       <c r="U32">
         <v>0.2358</v>
       </c>
       <c r="V32">
-        <v>0.008822792131380347</v>
+        <v>0.008538185933593883</v>
       </c>
       <c r="W32">
-        <v>0.2337195856154205</v>
+        <v>0.2337866957568586</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>0.05881861420920231</v>
+        <v>0.05692123955729256</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1527631385823995</v>
+        <v>0.1546631385823995</v>
       </c>
       <c r="C33">
-        <v>180.4556181625423</v>
+        <v>171.2136940565555</v>
       </c>
       <c r="D33">
-        <v>336.4896181625423</v>
+        <v>332.4816940565555</v>
       </c>
       <c r="E33">
-        <v>27.75399999999999</v>
+        <v>32.988</v>
       </c>
       <c r="F33">
-        <v>162.254</v>
+        <v>167.488</v>
       </c>
       <c r="G33">
         <v>6.22</v>
@@ -3993,37 +3993,37 @@
         <v>2.177777777777806</v>
       </c>
       <c r="M33">
-        <v>38.2594932</v>
+        <v>39.4936704</v>
       </c>
       <c r="N33">
-        <v>-36.0817154222222</v>
+        <v>-37.31589262222219</v>
       </c>
       <c r="O33">
-        <v>-5.412257313333329</v>
+        <v>-5.597383893333329</v>
       </c>
       <c r="P33">
-        <v>-30.66945810888887</v>
+        <v>-31.71850872888886</v>
       </c>
       <c r="Q33">
-        <v>141.9305418911111</v>
+        <v>140.8814912711111</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1163612505764831</v>
+        <v>0.1173989160261373</v>
       </c>
       <c r="T33">
-        <v>0.9196496375950424</v>
+        <v>0.93317389697144</v>
       </c>
       <c r="U33">
         <v>0.2358</v>
       </c>
       <c r="V33">
-        <v>0.008538185933593883</v>
+        <v>0.008271367623169074</v>
       </c>
       <c r="W33">
-        <v>0.2337866957568586</v>
+        <v>0.2338496115144567</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>0.05692123955729256</v>
+        <v>0.05514245082112712</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1546631385823995</v>
+        <v>0.1565631385823995</v>
       </c>
       <c r="C34">
-        <v>171.2136940565555</v>
+        <v>162.0661227939537</v>
       </c>
       <c r="D34">
-        <v>332.4816940565555</v>
+        <v>328.5681227939537</v>
       </c>
       <c r="E34">
-        <v>32.988</v>
+        <v>38.22200000000001</v>
       </c>
       <c r="F34">
-        <v>167.488</v>
+        <v>172.722</v>
       </c>
       <c r="G34">
         <v>6.22</v>
@@ -4075,37 +4075,37 @@
         <v>2.177777777777806</v>
       </c>
       <c r="M34">
-        <v>39.4936704</v>
+        <v>40.7278476</v>
       </c>
       <c r="N34">
-        <v>-37.31589262222219</v>
+        <v>-38.5500698222222</v>
       </c>
       <c r="O34">
-        <v>-5.597383893333329</v>
+        <v>-5.782510473333329</v>
       </c>
       <c r="P34">
-        <v>-31.71850872888886</v>
+        <v>-32.76755934888887</v>
       </c>
       <c r="Q34">
-        <v>140.8814912711111</v>
+        <v>139.8324406511111</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1173989160261373</v>
+        <v>0.1184675565638408</v>
       </c>
       <c r="T34">
-        <v>0.93317389697144</v>
+        <v>0.9471018655829541</v>
       </c>
       <c r="U34">
         <v>0.2358</v>
       </c>
       <c r="V34">
-        <v>0.008271367623169074</v>
+        <v>0.008020720119436678</v>
       </c>
       <c r="W34">
-        <v>0.2338496115144567</v>
+        <v>0.2339087141958368</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>0.05514245082112712</v>
+        <v>0.0534714674629112</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1565631385823995</v>
+        <v>0.1584631385823995</v>
       </c>
       <c r="C35">
-        <v>162.0661227939537</v>
+        <v>153.009611314925</v>
       </c>
       <c r="D35">
-        <v>328.5681227939537</v>
+        <v>324.745611314925</v>
       </c>
       <c r="E35">
-        <v>38.22200000000001</v>
+        <v>43.45600000000002</v>
       </c>
       <c r="F35">
-        <v>172.722</v>
+        <v>177.956</v>
       </c>
       <c r="G35">
         <v>6.22</v>
@@ -4157,37 +4157,37 @@
         <v>2.177777777777806</v>
       </c>
       <c r="M35">
-        <v>40.7278476</v>
+        <v>41.96202480000001</v>
       </c>
       <c r="N35">
-        <v>-38.5500698222222</v>
+        <v>-39.7842470222222</v>
       </c>
       <c r="O35">
-        <v>-5.782510473333329</v>
+        <v>-5.96763705333333</v>
       </c>
       <c r="P35">
-        <v>-32.76755934888887</v>
+        <v>-33.81660996888887</v>
       </c>
       <c r="Q35">
-        <v>139.8324406511111</v>
+        <v>138.7833900311111</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1184675565638408</v>
+        <v>0.1195685801481415</v>
       </c>
       <c r="T35">
-        <v>0.9471018655829541</v>
+        <v>0.9614518938493626</v>
       </c>
       <c r="U35">
         <v>0.2358</v>
       </c>
       <c r="V35">
-        <v>0.008020720119436678</v>
+        <v>0.007784816586512068</v>
       </c>
       <c r="W35">
-        <v>0.2339087141958368</v>
+        <v>0.2339643402489004</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>0.0534714674629112</v>
+        <v>0.05189877724341374</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1584631385823995</v>
+        <v>0.1603631385823995</v>
       </c>
       <c r="C36">
-        <v>153.009611314925</v>
+        <v>144.0410180411686</v>
       </c>
       <c r="D36">
-        <v>324.745611314925</v>
+        <v>321.0110180411686</v>
       </c>
       <c r="E36">
-        <v>43.45600000000002</v>
+        <v>48.69</v>
       </c>
       <c r="F36">
-        <v>177.956</v>
+        <v>183.19</v>
       </c>
       <c r="G36">
         <v>6.22</v>
@@ -4239,37 +4239,37 @@
         <v>2.177777777777806</v>
       </c>
       <c r="M36">
-        <v>41.96202480000001</v>
+        <v>43.196202</v>
       </c>
       <c r="N36">
-        <v>-39.7842470222222</v>
+        <v>-41.01842422222219</v>
       </c>
       <c r="O36">
-        <v>-5.96763705333333</v>
+        <v>-6.152763633333329</v>
       </c>
       <c r="P36">
-        <v>-33.81660996888887</v>
+        <v>-34.86566058888886</v>
       </c>
       <c r="Q36">
-        <v>138.7833900311111</v>
+        <v>137.7343394111111</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1195685801481415</v>
+        <v>0.1207034813811898</v>
       </c>
       <c r="T36">
-        <v>0.9614518938493626</v>
+        <v>0.976243461447045</v>
       </c>
       <c r="U36">
         <v>0.2358</v>
       </c>
       <c r="V36">
-        <v>0.007784816586512068</v>
+        <v>0.007562393255468867</v>
       </c>
       <c r="W36">
-        <v>0.2339643402489004</v>
+        <v>0.2340167876703605</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>0.05189877724341374</v>
+        <v>0.05041595503645913</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1603631385823995</v>
+        <v>0.1622631385823995</v>
       </c>
       <c r="C37">
-        <v>144.0410180411686</v>
+        <v>135.1573442646943</v>
       </c>
       <c r="D37">
-        <v>321.0110180411686</v>
+        <v>317.3613442646943</v>
       </c>
       <c r="E37">
-        <v>48.69</v>
+        <v>53.92400000000001</v>
       </c>
       <c r="F37">
-        <v>183.19</v>
+        <v>188.424</v>
       </c>
       <c r="G37">
         <v>6.22</v>
@@ -4321,37 +4321,37 @@
         <v>2.177777777777806</v>
       </c>
       <c r="M37">
-        <v>43.196202</v>
+        <v>44.4303792</v>
       </c>
       <c r="N37">
-        <v>-41.01842422222219</v>
+        <v>-42.2526014222222</v>
       </c>
       <c r="O37">
-        <v>-6.152763633333329</v>
+        <v>-6.337890213333329</v>
       </c>
       <c r="P37">
-        <v>-34.86566058888886</v>
+        <v>-35.91471120888887</v>
       </c>
       <c r="Q37">
-        <v>137.7343394111111</v>
+        <v>136.6852887911111</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1207034813811898</v>
+        <v>0.1218738482777709</v>
       </c>
       <c r="T37">
-        <v>0.976243461447045</v>
+        <v>0.9914972655321551</v>
       </c>
       <c r="U37">
         <v>0.2358</v>
       </c>
       <c r="V37">
-        <v>0.007562393255468867</v>
+        <v>0.007352326776150287</v>
       </c>
       <c r="W37">
-        <v>0.2340167876703605</v>
+        <v>0.2340663213461838</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>0.05041595503645913</v>
+        <v>0.04901551184100195</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1622631385823995</v>
+        <v>0.1641631385823995</v>
       </c>
       <c r="C38">
-        <v>135.1573442646943</v>
+        <v>126.3557261174377</v>
       </c>
       <c r="D38">
-        <v>317.3613442646943</v>
+        <v>313.7937261174376</v>
       </c>
       <c r="E38">
-        <v>53.92399999999998</v>
+        <v>59.15799999999999</v>
       </c>
       <c r="F38">
-        <v>188.424</v>
+        <v>193.658</v>
       </c>
       <c r="G38">
         <v>6.22</v>
@@ -4403,37 +4403,37 @@
         <v>2.177777777777806</v>
       </c>
       <c r="M38">
-        <v>44.4303792</v>
+        <v>45.6645564</v>
       </c>
       <c r="N38">
-        <v>-42.25260142222219</v>
+        <v>-43.4867786222222</v>
       </c>
       <c r="O38">
-        <v>-6.337890213333329</v>
+        <v>-6.523016793333329</v>
       </c>
       <c r="P38">
-        <v>-35.91471120888886</v>
+        <v>-36.96376182888887</v>
       </c>
       <c r="Q38">
-        <v>136.6852887911111</v>
+        <v>135.6362381711111</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1218738482777709</v>
+        <v>0.1230813696790053</v>
       </c>
       <c r="T38">
-        <v>0.9914972655321551</v>
+        <v>1.007235317365999</v>
       </c>
       <c r="U38">
         <v>0.2358</v>
       </c>
       <c r="V38">
-        <v>0.007352326776150288</v>
+        <v>0.007153615241659739</v>
       </c>
       <c r="W38">
-        <v>0.2340663213461838</v>
+        <v>0.2341131775260167</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>0.04901551184100195</v>
+        <v>0.04769076827773155</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1641631385823995</v>
+        <v>0.1660631385823995</v>
       </c>
       <c r="C39">
-        <v>126.3557261174377</v>
+        <v>117.6334270764966</v>
       </c>
       <c r="D39">
-        <v>313.7937261174376</v>
+        <v>310.3054270764965</v>
       </c>
       <c r="E39">
-        <v>59.15799999999999</v>
+        <v>64.392</v>
       </c>
       <c r="F39">
-        <v>193.658</v>
+        <v>198.892</v>
       </c>
       <c r="G39">
         <v>6.22</v>
@@ -4485,37 +4485,37 @@
         <v>2.177777777777806</v>
       </c>
       <c r="M39">
-        <v>45.6645564</v>
+        <v>46.8987336</v>
       </c>
       <c r="N39">
-        <v>-43.4867786222222</v>
+        <v>-44.72095582222219</v>
       </c>
       <c r="O39">
-        <v>-6.523016793333329</v>
+        <v>-6.708143373333329</v>
       </c>
       <c r="P39">
-        <v>-36.96376182888887</v>
+        <v>-38.01281244888887</v>
       </c>
       <c r="Q39">
-        <v>135.6362381711111</v>
+        <v>134.5871875511111</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1230813696790053</v>
+        <v>0.1243278433835054</v>
       </c>
       <c r="T39">
-        <v>1.007235317365999</v>
+        <v>1.023481048291257</v>
       </c>
       <c r="U39">
         <v>0.2358</v>
       </c>
       <c r="V39">
-        <v>0.007153615241659739</v>
+        <v>0.006965362208984483</v>
       </c>
       <c r="W39">
-        <v>0.2341131775260167</v>
+        <v>0.2341575675911215</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>0.04769076827773155</v>
+        <v>0.04643574805989659</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1660631385823995</v>
+        <v>0.1679631385823995</v>
       </c>
       <c r="C40">
-        <v>117.6334270764966</v>
+        <v>108.9878309637654</v>
       </c>
       <c r="D40">
-        <v>310.3054270764965</v>
+        <v>306.8938309637654</v>
       </c>
       <c r="E40">
-        <v>64.392</v>
+        <v>69.626</v>
       </c>
       <c r="F40">
-        <v>198.892</v>
+        <v>204.126</v>
       </c>
       <c r="G40">
         <v>6.22</v>
@@ -4567,37 +4567,37 @@
         <v>2.177777777777806</v>
       </c>
       <c r="M40">
-        <v>46.8987336</v>
+        <v>48.1329108</v>
       </c>
       <c r="N40">
-        <v>-44.72095582222219</v>
+        <v>-45.9551330222222</v>
       </c>
       <c r="O40">
-        <v>-6.708143373333329</v>
+        <v>-6.89326995333333</v>
       </c>
       <c r="P40">
-        <v>-38.01281244888887</v>
+        <v>-39.06186306888887</v>
       </c>
       <c r="Q40">
-        <v>134.5871875511111</v>
+        <v>133.5381369311111</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1243278433835054</v>
+        <v>0.125615185078317</v>
       </c>
       <c r="T40">
-        <v>1.023481048291257</v>
+        <v>1.040259426132097</v>
       </c>
       <c r="U40">
         <v>0.2358</v>
       </c>
       <c r="V40">
-        <v>0.006965362208984483</v>
+        <v>0.006786763177984882</v>
       </c>
       <c r="W40">
-        <v>0.2341575675911215</v>
+        <v>0.2341996812426312</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.04643574805989659</v>
+        <v>0.04524508785323256</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1679631385823995</v>
+        <v>0.1698631385823995</v>
       </c>
       <c r="C41">
-        <v>108.9878309637654</v>
+        <v>100.4164354023342</v>
       </c>
       <c r="D41">
-        <v>306.8938309637654</v>
+        <v>303.5564354023342</v>
       </c>
       <c r="E41">
-        <v>69.626</v>
+        <v>74.86000000000001</v>
       </c>
       <c r="F41">
-        <v>204.126</v>
+        <v>209.36</v>
       </c>
       <c r="G41">
         <v>6.22</v>
@@ -4649,37 +4649,37 @@
         <v>2.177777777777806</v>
       </c>
       <c r="M41">
-        <v>48.1329108</v>
+        <v>49.367088</v>
       </c>
       <c r="N41">
-        <v>-45.9551330222222</v>
+        <v>-47.1893102222222</v>
       </c>
       <c r="O41">
-        <v>-6.89326995333333</v>
+        <v>-7.078396533333329</v>
       </c>
       <c r="P41">
-        <v>-39.06186306888887</v>
+        <v>-40.11091368888887</v>
       </c>
       <c r="Q41">
-        <v>133.5381369311111</v>
+        <v>132.4890863111111</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.125615185078317</v>
+        <v>0.1269454381629556</v>
       </c>
       <c r="T41">
-        <v>1.040259426132097</v>
+        <v>1.057597083234299</v>
       </c>
       <c r="U41">
         <v>0.2358</v>
       </c>
       <c r="V41">
-        <v>0.006786763177984882</v>
+        <v>0.006617094098535259</v>
       </c>
       <c r="W41">
-        <v>0.2341996812426312</v>
+        <v>0.2342396892115654</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.04524508785323256</v>
+        <v>0.04411396065690176</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1698631385823995</v>
+        <v>0.1717631385823995</v>
       </c>
       <c r="C42">
-        <v>100.4164354023342</v>
+        <v>91.91684569525387</v>
       </c>
       <c r="D42">
-        <v>303.5564354023342</v>
+        <v>300.2908456952538</v>
       </c>
       <c r="E42">
-        <v>74.86000000000001</v>
+        <v>80.09399999999999</v>
       </c>
       <c r="F42">
-        <v>209.36</v>
+        <v>214.594</v>
       </c>
       <c r="G42">
         <v>6.22</v>
@@ -4731,37 +4731,37 @@
         <v>2.177777777777806</v>
       </c>
       <c r="M42">
-        <v>49.367088</v>
+        <v>50.6012652</v>
       </c>
       <c r="N42">
-        <v>-47.1893102222222</v>
+        <v>-48.42348742222219</v>
       </c>
       <c r="O42">
-        <v>-7.078396533333329</v>
+        <v>-7.263523113333329</v>
       </c>
       <c r="P42">
-        <v>-40.11091368888887</v>
+        <v>-41.15996430888887</v>
       </c>
       <c r="Q42">
-        <v>132.4890863111111</v>
+        <v>131.4400356911111</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1269454381629556</v>
+        <v>0.1283207845724972</v>
       </c>
       <c r="T42">
-        <v>1.057597083234299</v>
+        <v>1.075522457526406</v>
       </c>
       <c r="U42">
         <v>0.2358</v>
       </c>
       <c r="V42">
-        <v>0.006617094098535259</v>
+        <v>0.006455701559546595</v>
       </c>
       <c r="W42">
-        <v>0.2342396892115654</v>
+        <v>0.2342777455722589</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.04411396065690176</v>
+        <v>0.0430380103969773</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1717631385823995</v>
+        <v>0.1736631385823995</v>
       </c>
       <c r="C43">
-        <v>91.91684569525387</v>
+        <v>83.48676909520142</v>
       </c>
       <c r="D43">
-        <v>300.2908456952538</v>
+        <v>297.0947690952014</v>
       </c>
       <c r="E43">
-        <v>80.09399999999999</v>
+        <v>85.328</v>
       </c>
       <c r="F43">
-        <v>214.594</v>
+        <v>219.828</v>
       </c>
       <c r="G43">
         <v>6.22</v>
@@ -4813,37 +4813,37 @@
         <v>2.177777777777806</v>
       </c>
       <c r="M43">
-        <v>50.6012652</v>
+        <v>51.83544240000001</v>
       </c>
       <c r="N43">
-        <v>-48.42348742222219</v>
+        <v>-49.6576646222222</v>
       </c>
       <c r="O43">
-        <v>-7.263523113333329</v>
+        <v>-7.44864969333333</v>
       </c>
       <c r="P43">
-        <v>-41.15996430888887</v>
+        <v>-42.20901492888887</v>
       </c>
       <c r="Q43">
-        <v>131.4400356911111</v>
+        <v>130.3909850711111</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1283207845724972</v>
+        <v>0.1297435567202989</v>
       </c>
       <c r="T43">
-        <v>1.075522457526406</v>
+        <v>1.094065948173413</v>
       </c>
       <c r="U43">
         <v>0.2358</v>
       </c>
       <c r="V43">
-        <v>0.006455701559546595</v>
+        <v>0.00630199437955739</v>
       </c>
       <c r="W43">
-        <v>0.2342777455722589</v>
+        <v>0.2343139897253004</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.0430380103969773</v>
+        <v>0.04201329586371594</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1736631385823995</v>
+        <v>0.1755631385823995</v>
       </c>
       <c r="C44">
-        <v>83.48676909520145</v>
+        <v>75.12400943622933</v>
       </c>
       <c r="D44">
-        <v>297.0947690952014</v>
+        <v>293.9660094362293</v>
       </c>
       <c r="E44">
-        <v>85.32799999999997</v>
+        <v>90.56199999999998</v>
       </c>
       <c r="F44">
-        <v>219.828</v>
+        <v>225.062</v>
       </c>
       <c r="G44">
         <v>6.22</v>
@@ -4895,37 +4895,37 @@
         <v>2.177777777777806</v>
       </c>
       <c r="M44">
-        <v>51.8354424</v>
+        <v>53.0696196</v>
       </c>
       <c r="N44">
-        <v>-49.65766462222219</v>
+        <v>-50.89184182222219</v>
       </c>
       <c r="O44">
-        <v>-7.448649693333328</v>
+        <v>-7.633776273333329</v>
       </c>
       <c r="P44">
-        <v>-42.20901492888886</v>
+        <v>-43.25806554888887</v>
       </c>
       <c r="Q44">
-        <v>130.3909850711111</v>
+        <v>129.3419344511111</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1297435567202989</v>
+        <v>0.131216250697848</v>
       </c>
       <c r="T44">
-        <v>1.094065948173412</v>
+        <v>1.113260087615051</v>
       </c>
       <c r="U44">
         <v>0.2358</v>
       </c>
       <c r="V44">
-        <v>0.006301994379557391</v>
+        <v>0.006155436370730474</v>
       </c>
       <c r="W44">
-        <v>0.2343139897253004</v>
+        <v>0.2343485481037818</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.04201329586371594</v>
+        <v>0.04103624247153648</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1755631385823995</v>
+        <v>0.1774631385823995</v>
       </c>
       <c r="C45">
-        <v>75.12400943622933</v>
+        <v>66.82646210118287</v>
       </c>
       <c r="D45">
-        <v>293.9660094362293</v>
+        <v>290.9024621011828</v>
       </c>
       <c r="E45">
-        <v>90.56199999999998</v>
+        <v>95.79599999999999</v>
       </c>
       <c r="F45">
-        <v>225.062</v>
+        <v>230.296</v>
       </c>
       <c r="G45">
         <v>6.22</v>
@@ -4977,37 +4977,37 @@
         <v>2.177777777777806</v>
       </c>
       <c r="M45">
-        <v>53.0696196</v>
+        <v>54.3037968</v>
       </c>
       <c r="N45">
-        <v>-50.89184182222219</v>
+        <v>-52.1260190222222</v>
       </c>
       <c r="O45">
-        <v>-7.633776273333329</v>
+        <v>-7.818902853333329</v>
       </c>
       <c r="P45">
-        <v>-43.25806554888887</v>
+        <v>-44.30711616888887</v>
       </c>
       <c r="Q45">
-        <v>129.3419344511111</v>
+        <v>128.2928838311111</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.131216250697848</v>
+        <v>0.132741540888881</v>
       </c>
       <c r="T45">
-        <v>1.113260087615051</v>
+        <v>1.133139732036749</v>
       </c>
       <c r="U45">
         <v>0.2358</v>
       </c>
       <c r="V45">
-        <v>0.006155436370730474</v>
+        <v>0.006015540089577508</v>
       </c>
       <c r="W45">
-        <v>0.2343485481037818</v>
+        <v>0.2343815356468776</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.04103624247153648</v>
+        <v>0.04010360059718343</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1774631385823995</v>
+        <v>0.1793631385823995</v>
       </c>
       <c r="C46">
-        <v>66.82646210118287</v>
+        <v>58.59210930055306</v>
       </c>
       <c r="D46">
-        <v>290.9024621011828</v>
+        <v>287.902109300553</v>
       </c>
       <c r="E46">
-        <v>95.79599999999999</v>
+        <v>101.03</v>
       </c>
       <c r="F46">
-        <v>230.296</v>
+        <v>235.53</v>
       </c>
       <c r="G46">
         <v>6.22</v>
@@ -5059,37 +5059,37 @@
         <v>2.177777777777806</v>
       </c>
       <c r="M46">
-        <v>54.3037968</v>
+        <v>55.53797400000001</v>
       </c>
       <c r="N46">
-        <v>-52.1260190222222</v>
+        <v>-53.3601962222222</v>
       </c>
       <c r="O46">
-        <v>-7.818902853333329</v>
+        <v>-8.004029433333329</v>
       </c>
       <c r="P46">
-        <v>-44.30711616888887</v>
+        <v>-45.35616678888887</v>
       </c>
       <c r="Q46">
-        <v>128.2928838311111</v>
+        <v>127.2438332111111</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.132741540888881</v>
+        <v>0.1343222961777697</v>
       </c>
       <c r="T46">
-        <v>1.133139732036749</v>
+        <v>1.153742272619235</v>
       </c>
       <c r="U46">
         <v>0.2358</v>
       </c>
       <c r="V46">
-        <v>0.006015540089577508</v>
+        <v>0.00588186142092023</v>
       </c>
       <c r="W46">
-        <v>0.2343815356468776</v>
+        <v>0.234413057076947</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.04010360059718343</v>
+        <v>0.03921240947280158</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1793631385823995</v>
+        <v>0.1812631385823995</v>
       </c>
       <c r="C47">
-        <v>58.59210930055306</v>
+        <v>50.41901564050863</v>
       </c>
       <c r="D47">
-        <v>287.902109300553</v>
+        <v>284.9630156405086</v>
       </c>
       <c r="E47">
-        <v>101.03</v>
+        <v>106.264</v>
       </c>
       <c r="F47">
-        <v>235.53</v>
+        <v>240.764</v>
       </c>
       <c r="G47">
         <v>6.22</v>
@@ -5141,37 +5141,37 @@
         <v>2.177777777777806</v>
       </c>
       <c r="M47">
-        <v>55.53797400000001</v>
+        <v>56.7721512</v>
       </c>
       <c r="N47">
-        <v>-53.3601962222222</v>
+        <v>-54.5943734222222</v>
       </c>
       <c r="O47">
-        <v>-8.004029433333329</v>
+        <v>-8.18915601333333</v>
       </c>
       <c r="P47">
-        <v>-45.35616678888887</v>
+        <v>-46.40521740888887</v>
       </c>
       <c r="Q47">
-        <v>127.2438332111111</v>
+        <v>126.1947825911111</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1343222961777697</v>
+        <v>0.1359615979588395</v>
       </c>
       <c r="T47">
-        <v>1.153742272619235</v>
+        <v>1.175107870260332</v>
       </c>
       <c r="U47">
         <v>0.2358</v>
       </c>
       <c r="V47">
-        <v>0.00588186142092023</v>
+        <v>0.00575399486829153</v>
       </c>
       <c r="W47">
-        <v>0.234413057076947</v>
+        <v>0.2344432080100569</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.03921240947280158</v>
+        <v>0.03835996578861023</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1812631385823995</v>
+        <v>0.1831631385823995</v>
       </c>
       <c r="C48">
-        <v>50.41901564050863</v>
+        <v>42.30532395965133</v>
       </c>
       <c r="D48">
-        <v>284.9630156405086</v>
+        <v>282.0833239596513</v>
       </c>
       <c r="E48">
-        <v>106.264</v>
+        <v>111.498</v>
       </c>
       <c r="F48">
-        <v>240.764</v>
+        <v>245.998</v>
       </c>
       <c r="G48">
         <v>6.22</v>
@@ -5223,37 +5223,37 @@
         <v>2.177777777777806</v>
       </c>
       <c r="M48">
-        <v>56.7721512</v>
+        <v>58.0063284</v>
       </c>
       <c r="N48">
-        <v>-54.5943734222222</v>
+        <v>-55.8285506222222</v>
       </c>
       <c r="O48">
-        <v>-8.18915601333333</v>
+        <v>-8.374282593333328</v>
       </c>
       <c r="P48">
-        <v>-46.40521740888887</v>
+        <v>-47.45426802888887</v>
       </c>
       <c r="Q48">
-        <v>126.1947825911111</v>
+        <v>125.1457319711111</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1359615979588395</v>
+        <v>0.137662760184478</v>
       </c>
       <c r="T48">
-        <v>1.175107870260332</v>
+        <v>1.197279716869017</v>
       </c>
       <c r="U48">
         <v>0.2358</v>
       </c>
       <c r="V48">
-        <v>0.00575399486829153</v>
+        <v>0.005631569445561923</v>
       </c>
       <c r="W48">
-        <v>0.2344432080100569</v>
+        <v>0.2344720759247365</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.03835996578861023</v>
+        <v>0.03754379630374616</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1831631385823995</v>
+        <v>0.1850631385823995</v>
       </c>
       <c r="C49">
-        <v>42.30532395965133</v>
+        <v>34.24925141567579</v>
       </c>
       <c r="D49">
-        <v>282.0833239596513</v>
+        <v>279.2612514156758</v>
       </c>
       <c r="E49">
-        <v>111.498</v>
+        <v>116.732</v>
       </c>
       <c r="F49">
-        <v>245.998</v>
+        <v>251.232</v>
       </c>
       <c r="G49">
         <v>6.22</v>
@@ -5305,37 +5305,37 @@
         <v>2.177777777777806</v>
       </c>
       <c r="M49">
-        <v>58.0063284</v>
+        <v>59.2405056</v>
       </c>
       <c r="N49">
-        <v>-55.8285506222222</v>
+        <v>-57.06272782222219</v>
       </c>
       <c r="O49">
-        <v>-8.374282593333328</v>
+        <v>-8.559409173333329</v>
       </c>
       <c r="P49">
-        <v>-47.45426802888887</v>
+        <v>-48.50331864888886</v>
       </c>
       <c r="Q49">
-        <v>125.1457319711111</v>
+        <v>124.0966813511111</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.137662760184478</v>
+        <v>0.1394293517264872</v>
       </c>
       <c r="T49">
-        <v>1.197279716869017</v>
+        <v>1.220304326808806</v>
       </c>
       <c r="U49">
         <v>0.2358</v>
       </c>
       <c r="V49">
-        <v>0.005631569445561923</v>
+        <v>0.005514245082112717</v>
       </c>
       <c r="W49">
-        <v>0.2344720759247365</v>
+        <v>0.2344997410096378</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.03754379630374616</v>
+        <v>0.03676163388075149</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1850631385823995</v>
+        <v>0.1869631385823995</v>
       </c>
       <c r="C50">
-        <v>34.24925141567593</v>
+        <v>26.24908580460647</v>
       </c>
       <c r="D50">
-        <v>279.2612514156759</v>
+        <v>276.4950858046064</v>
       </c>
       <c r="E50">
-        <v>116.732</v>
+        <v>121.966</v>
       </c>
       <c r="F50">
-        <v>251.232</v>
+        <v>256.466</v>
       </c>
       <c r="G50">
         <v>6.22</v>
@@ -5387,37 +5387,37 @@
         <v>2.177777777777806</v>
       </c>
       <c r="M50">
-        <v>59.2405056</v>
+        <v>60.4746828</v>
       </c>
       <c r="N50">
-        <v>-57.06272782222219</v>
+        <v>-58.2969050222222</v>
       </c>
       <c r="O50">
-        <v>-8.559409173333329</v>
+        <v>-8.744535753333329</v>
       </c>
       <c r="P50">
-        <v>-48.50331864888886</v>
+        <v>-49.55236926888887</v>
       </c>
       <c r="Q50">
-        <v>124.0966813511111</v>
+        <v>123.0476307311111</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1394293517264872</v>
+        <v>0.141265221368183</v>
       </c>
       <c r="T50">
-        <v>1.220304326808806</v>
+        <v>1.244231862628587</v>
       </c>
       <c r="U50">
         <v>0.2358</v>
       </c>
       <c r="V50">
-        <v>0.005514245082112717</v>
+        <v>0.005401709468192048</v>
       </c>
       <c r="W50">
-        <v>0.2344997410096378</v>
+        <v>0.2345262769074003</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.03676163388075149</v>
+        <v>0.03601139645461371</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1869631385823995</v>
+        <v>0.1888631385823995</v>
       </c>
       <c r="C51">
-        <v>26.24908580460647</v>
+        <v>18.30318209664244</v>
       </c>
       <c r="D51">
-        <v>276.4950858046064</v>
+        <v>273.7831820966424</v>
       </c>
       <c r="E51">
-        <v>121.966</v>
+        <v>127.2</v>
       </c>
       <c r="F51">
-        <v>256.466</v>
+        <v>261.7</v>
       </c>
       <c r="G51">
         <v>6.22</v>
@@ -5469,37 +5469,37 @@
         <v>2.177777777777806</v>
       </c>
       <c r="M51">
-        <v>60.4746828</v>
+        <v>61.70886</v>
       </c>
       <c r="N51">
-        <v>-58.2969050222222</v>
+        <v>-59.5310822222222</v>
       </c>
       <c r="O51">
-        <v>-8.744535753333329</v>
+        <v>-8.929662333333329</v>
       </c>
       <c r="P51">
-        <v>-49.55236926888887</v>
+        <v>-50.60141988888887</v>
       </c>
       <c r="Q51">
-        <v>123.0476307311111</v>
+        <v>121.9985801111111</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.141265221368183</v>
+        <v>0.1431745257955467</v>
       </c>
       <c r="T51">
-        <v>1.244231862628587</v>
+        <v>1.269116499881158</v>
       </c>
       <c r="U51">
         <v>0.2358</v>
       </c>
       <c r="V51">
-        <v>0.005401709468192048</v>
+        <v>0.005293675278828207</v>
       </c>
       <c r="W51">
-        <v>0.2345262769074003</v>
+        <v>0.2345517513692523</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.03601139645461371</v>
+        <v>0.03529116852552139</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1888631385823995</v>
+        <v>0.1907631385823995</v>
       </c>
       <c r="C52">
-        <v>18.30318209664244</v>
+        <v>10.40995917388432</v>
       </c>
       <c r="D52">
-        <v>273.7831820966424</v>
+        <v>271.1239591738843</v>
       </c>
       <c r="E52">
-        <v>127.2</v>
+        <v>132.434</v>
       </c>
       <c r="F52">
-        <v>261.7</v>
+        <v>266.934</v>
       </c>
       <c r="G52">
         <v>6.22</v>
@@ -5551,37 +5551,37 @@
         <v>2.177777777777806</v>
       </c>
       <c r="M52">
-        <v>61.70886</v>
+        <v>62.94303719999999</v>
       </c>
       <c r="N52">
-        <v>-59.5310822222222</v>
+        <v>-60.76525942222219</v>
       </c>
       <c r="O52">
-        <v>-8.929662333333329</v>
+        <v>-9.114788913333328</v>
       </c>
       <c r="P52">
-        <v>-50.60141988888887</v>
+        <v>-51.65047050888886</v>
       </c>
       <c r="Q52">
-        <v>121.9985801111111</v>
+        <v>120.9495294911111</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1431745257955467</v>
+        <v>0.145161761015864</v>
       </c>
       <c r="T52">
-        <v>1.269116499881158</v>
+        <v>1.295016836613427</v>
       </c>
       <c r="U52">
         <v>0.2358</v>
       </c>
       <c r="V52">
-        <v>0.005293675278828207</v>
+        <v>0.00518987772434138</v>
       </c>
       <c r="W52">
-        <v>0.2345517513692523</v>
+        <v>0.2345762268326003</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.03529116852552139</v>
+        <v>0.03459918482894253</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1907631385823995</v>
+        <v>0.1926631385823995</v>
       </c>
       <c r="C53">
-        <v>10.40995917388432</v>
+        <v>2.567896756349228</v>
       </c>
       <c r="D53">
-        <v>271.1239591738843</v>
+        <v>268.5158967563492</v>
       </c>
       <c r="E53">
-        <v>132.434</v>
+        <v>137.668</v>
       </c>
       <c r="F53">
-        <v>266.934</v>
+        <v>272.168</v>
       </c>
       <c r="G53">
         <v>6.22</v>
@@ -5633,37 +5633,37 @@
         <v>2.177777777777806</v>
       </c>
       <c r="M53">
-        <v>62.94303719999999</v>
+        <v>64.17721440000001</v>
       </c>
       <c r="N53">
-        <v>-60.76525942222219</v>
+        <v>-61.99943662222221</v>
       </c>
       <c r="O53">
-        <v>-9.114788913333328</v>
+        <v>-9.29991549333333</v>
       </c>
       <c r="P53">
-        <v>-51.65047050888886</v>
+        <v>-52.69952112888888</v>
       </c>
       <c r="Q53">
-        <v>120.9495294911111</v>
+        <v>119.9004788711111</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.145161761015864</v>
+        <v>0.1472317977036945</v>
       </c>
       <c r="T53">
-        <v>1.295016836613427</v>
+        <v>1.321996354042873</v>
       </c>
       <c r="U53">
         <v>0.2358</v>
       </c>
       <c r="V53">
-        <v>0.00518987772434138</v>
+        <v>0.00509007238348866</v>
       </c>
       <c r="W53">
-        <v>0.2345762268326003</v>
+        <v>0.2345997609319734</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.03459918482894253</v>
+        <v>0.03393381588992439</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1926631385823995</v>
+        <v>0.1945631385823995</v>
       </c>
       <c r="C54">
-        <v>2.567896756349228</v>
+        <v>-5.22446749628557</v>
       </c>
       <c r="D54">
-        <v>268.5158967563492</v>
+        <v>265.9575325037144</v>
       </c>
       <c r="E54">
-        <v>137.668</v>
+        <v>142.902</v>
       </c>
       <c r="F54">
-        <v>272.168</v>
+        <v>277.402</v>
       </c>
       <c r="G54">
         <v>6.22</v>
@@ -5715,37 +5715,37 @@
         <v>2.177777777777806</v>
       </c>
       <c r="M54">
-        <v>64.17721440000001</v>
+        <v>65.4113916</v>
       </c>
       <c r="N54">
-        <v>-61.99943662222221</v>
+        <v>-63.2336138222222</v>
       </c>
       <c r="O54">
-        <v>-9.29991549333333</v>
+        <v>-9.485042073333329</v>
       </c>
       <c r="P54">
-        <v>-52.69952112888888</v>
+        <v>-53.74857174888886</v>
       </c>
       <c r="Q54">
-        <v>119.9004788711111</v>
+        <v>118.8514282511111</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1472317977036945</v>
+        <v>0.1493899210590922</v>
       </c>
       <c r="T54">
-        <v>1.321996354042873</v>
+        <v>1.350123936043786</v>
       </c>
       <c r="U54">
         <v>0.2358</v>
       </c>
       <c r="V54">
-        <v>0.00509007238348866</v>
+        <v>0.004994033281913403</v>
       </c>
       <c r="W54">
-        <v>0.2345997609319734</v>
+        <v>0.2346224069521248</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.03393381588992439</v>
+        <v>0.03329355521275601</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1945631385823995</v>
+        <v>0.1964631385823995</v>
       </c>
       <c r="C55">
-        <v>-5.22446749628557</v>
+        <v>-12.9685407188183</v>
       </c>
       <c r="D55">
-        <v>265.9575325037144</v>
+        <v>263.4474592811817</v>
       </c>
       <c r="E55">
-        <v>142.902</v>
+        <v>148.136</v>
       </c>
       <c r="F55">
-        <v>277.402</v>
+        <v>282.636</v>
       </c>
       <c r="G55">
         <v>6.22</v>
@@ -5797,37 +5797,37 @@
         <v>2.177777777777806</v>
       </c>
       <c r="M55">
-        <v>65.4113916</v>
+        <v>66.64556880000001</v>
       </c>
       <c r="N55">
-        <v>-63.2336138222222</v>
+        <v>-64.4677910222222</v>
       </c>
       <c r="O55">
-        <v>-9.485042073333329</v>
+        <v>-9.670168653333329</v>
       </c>
       <c r="P55">
-        <v>-53.74857174888886</v>
+        <v>-54.79762236888887</v>
       </c>
       <c r="Q55">
-        <v>118.8514282511111</v>
+        <v>117.8023776311111</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1493899210590922</v>
+        <v>0.1516418758647247</v>
       </c>
       <c r="T55">
-        <v>1.350123936043786</v>
+        <v>1.379474456392564</v>
       </c>
       <c r="U55">
         <v>0.2358</v>
       </c>
       <c r="V55">
-        <v>0.004994033281913403</v>
+        <v>0.004901551184100191</v>
       </c>
       <c r="W55">
-        <v>0.2346224069521248</v>
+        <v>0.2346442142307892</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.03329355521275601</v>
+        <v>0.0326770078940013</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1964631385823995</v>
+        <v>0.1983631385823995</v>
       </c>
       <c r="C56">
-        <v>-12.9685407188183</v>
+        <v>-20.66567742127864</v>
       </c>
       <c r="D56">
-        <v>263.4474592811817</v>
+        <v>260.9843225787213</v>
       </c>
       <c r="E56">
-        <v>148.136</v>
+        <v>153.37</v>
       </c>
       <c r="F56">
-        <v>282.636</v>
+        <v>287.87</v>
       </c>
       <c r="G56">
         <v>6.22</v>
@@ -5879,37 +5879,37 @@
         <v>2.177777777777806</v>
       </c>
       <c r="M56">
-        <v>66.64556880000001</v>
+        <v>67.879746</v>
       </c>
       <c r="N56">
-        <v>-64.4677910222222</v>
+        <v>-65.70196822222219</v>
       </c>
       <c r="O56">
-        <v>-9.670168653333329</v>
+        <v>-9.855295233333328</v>
       </c>
       <c r="P56">
-        <v>-54.79762236888887</v>
+        <v>-55.84667298888886</v>
       </c>
       <c r="Q56">
-        <v>117.8023776311111</v>
+        <v>116.7533270111111</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1516418758647247</v>
+        <v>0.1539939175506075</v>
       </c>
       <c r="T56">
-        <v>1.379474456392564</v>
+        <v>1.410129444312399</v>
       </c>
       <c r="U56">
         <v>0.2358</v>
       </c>
       <c r="V56">
-        <v>0.004901551184100191</v>
+        <v>0.004812432071662007</v>
       </c>
       <c r="W56">
-        <v>0.2346442142307892</v>
+        <v>0.2346652285175021</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.0326770078940013</v>
+        <v>0.03208288047774677</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1983631385823995</v>
+        <v>0.2002631385823995</v>
       </c>
       <c r="C57">
-        <v>-20.66567742127864</v>
+        <v>-28.31718192625124</v>
       </c>
       <c r="D57">
-        <v>260.9843225787213</v>
+        <v>258.5668180737488</v>
       </c>
       <c r="E57">
-        <v>153.37</v>
+        <v>158.604</v>
       </c>
       <c r="F57">
-        <v>287.87</v>
+        <v>293.104</v>
       </c>
       <c r="G57">
         <v>6.22</v>
@@ -5961,37 +5961,37 @@
         <v>2.177777777777806</v>
       </c>
       <c r="M57">
-        <v>67.879746</v>
+        <v>69.11392320000002</v>
       </c>
       <c r="N57">
-        <v>-65.70196822222219</v>
+        <v>-66.93614542222221</v>
       </c>
       <c r="O57">
-        <v>-9.855295233333328</v>
+        <v>-10.04042181333333</v>
       </c>
       <c r="P57">
-        <v>-55.84667298888886</v>
+        <v>-56.89572360888888</v>
       </c>
       <c r="Q57">
-        <v>116.7533270111111</v>
+        <v>115.7042763911111</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1539939175506075</v>
+        <v>0.1564528702222122</v>
       </c>
       <c r="T57">
-        <v>1.410129444312399</v>
+        <v>1.442177840774044</v>
       </c>
       <c r="U57">
         <v>0.2358</v>
       </c>
       <c r="V57">
-        <v>0.004812432071662007</v>
+        <v>0.004726495784668042</v>
       </c>
       <c r="W57">
-        <v>0.2346652285175021</v>
+        <v>0.2346854922939753</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.03208288047774677</v>
+        <v>0.03150997189778693</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.2002631385823995</v>
+        <v>0.2021631385823995</v>
       </c>
       <c r="C58">
-        <v>-28.31718192625124</v>
+        <v>-35.92431067197964</v>
       </c>
       <c r="D58">
-        <v>258.5668180737488</v>
+        <v>256.1936893280204</v>
       </c>
       <c r="E58">
-        <v>158.604</v>
+        <v>163.838</v>
       </c>
       <c r="F58">
-        <v>293.104</v>
+        <v>298.338</v>
       </c>
       <c r="G58">
         <v>6.22</v>
@@ -6043,37 +6043,37 @@
         <v>2.177777777777806</v>
       </c>
       <c r="M58">
-        <v>69.11392320000002</v>
+        <v>70.34810040000001</v>
       </c>
       <c r="N58">
-        <v>-66.93614542222221</v>
+        <v>-68.1703226222222</v>
       </c>
       <c r="O58">
-        <v>-10.04042181333333</v>
+        <v>-10.22554839333333</v>
       </c>
       <c r="P58">
-        <v>-56.89572360888888</v>
+        <v>-57.94477422888887</v>
       </c>
       <c r="Q58">
-        <v>115.7042763911111</v>
+        <v>114.6552257711111</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1564528702222122</v>
+        <v>0.1590261927855194</v>
       </c>
       <c r="T58">
-        <v>1.442177840774044</v>
+        <v>1.475716860326929</v>
       </c>
       <c r="U58">
         <v>0.2358</v>
       </c>
       <c r="V58">
-        <v>0.004726495784668042</v>
+        <v>0.004643574805989655</v>
       </c>
       <c r="W58">
-        <v>0.2346854922939753</v>
+        <v>0.2347050450607477</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.03150997189778693</v>
+        <v>0.03095716537326432</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.2021631385823995</v>
+        <v>0.2040631385823995</v>
       </c>
       <c r="C59">
-        <v>-35.92431067197964</v>
+        <v>-43.48827438979686</v>
       </c>
       <c r="D59">
-        <v>256.1936893280204</v>
+        <v>253.8637256102031</v>
       </c>
       <c r="E59">
-        <v>163.838</v>
+        <v>169.072</v>
       </c>
       <c r="F59">
-        <v>298.338</v>
+        <v>303.572</v>
       </c>
       <c r="G59">
         <v>6.22</v>
@@ -6125,37 +6125,37 @@
         <v>2.177777777777806</v>
       </c>
       <c r="M59">
-        <v>70.34810040000001</v>
+        <v>71.5822776</v>
       </c>
       <c r="N59">
-        <v>-68.1703226222222</v>
+        <v>-69.40449982222219</v>
       </c>
       <c r="O59">
-        <v>-10.22554839333333</v>
+        <v>-10.41067497333333</v>
       </c>
       <c r="P59">
-        <v>-57.94477422888887</v>
+        <v>-58.99382484888886</v>
       </c>
       <c r="Q59">
-        <v>114.6552257711111</v>
+        <v>113.6061751511111</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1590261927855194</v>
+        <v>0.161722054518508</v>
       </c>
       <c r="T59">
-        <v>1.475716860326929</v>
+        <v>1.510852976048999</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>0.004643574805989655</v>
+        <v>0.004563513171403627</v>
       </c>
       <c r="W59">
-        <v>0.2347050450607477</v>
+        <v>0.234723923594183</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.03095716537326432</v>
+        <v>0.03042342114269081</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.2040631385823995</v>
+        <v>0.2059631385823995</v>
       </c>
       <c r="C60">
-        <v>-43.4882743897968</v>
+        <v>-51.01024016380984</v>
       </c>
       <c r="D60">
-        <v>253.8637256102031</v>
+        <v>251.5757598361901</v>
       </c>
       <c r="E60">
-        <v>169.0719999999999</v>
+        <v>174.306</v>
       </c>
       <c r="F60">
-        <v>303.5719999999999</v>
+        <v>308.806</v>
       </c>
       <c r="G60">
         <v>6.22</v>
@@ -6207,37 +6207,37 @@
         <v>2.177777777777806</v>
       </c>
       <c r="M60">
-        <v>71.58227759999998</v>
+        <v>72.8164548</v>
       </c>
       <c r="N60">
-        <v>-69.40449982222218</v>
+        <v>-70.6386770222222</v>
       </c>
       <c r="O60">
-        <v>-10.41067497333333</v>
+        <v>-10.59580155333333</v>
       </c>
       <c r="P60">
-        <v>-58.99382484888885</v>
+        <v>-60.04287546888887</v>
       </c>
       <c r="Q60">
-        <v>113.6061751511111</v>
+        <v>112.5571245311111</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.161722054518508</v>
+        <v>0.1645494217018862</v>
       </c>
       <c r="T60">
-        <v>1.510852976048998</v>
+        <v>1.547703048635559</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>0.004563513171403628</v>
+        <v>0.004486165490532379</v>
       </c>
       <c r="W60">
-        <v>0.234723923594183</v>
+        <v>0.2347421621773325</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.03042342114269081</v>
+        <v>0.02990776993688249</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.2059631385823995</v>
+        <v>0.2078631385823995</v>
       </c>
       <c r="C61">
-        <v>-51.01024016380984</v>
+        <v>-58.49133338020067</v>
       </c>
       <c r="D61">
-        <v>251.5757598361901</v>
+        <v>249.3286666197993</v>
       </c>
       <c r="E61">
-        <v>174.306</v>
+        <v>179.54</v>
       </c>
       <c r="F61">
-        <v>308.806</v>
+        <v>314.04</v>
       </c>
       <c r="G61">
         <v>6.22</v>
@@ -6289,37 +6289,37 @@
         <v>2.177777777777806</v>
       </c>
       <c r="M61">
-        <v>72.8164548</v>
+        <v>74.05063199999999</v>
       </c>
       <c r="N61">
-        <v>-70.6386770222222</v>
+        <v>-71.87285422222219</v>
       </c>
       <c r="O61">
-        <v>-10.59580155333333</v>
+        <v>-10.78092813333333</v>
       </c>
       <c r="P61">
-        <v>-60.04287546888887</v>
+        <v>-61.09192608888886</v>
       </c>
       <c r="Q61">
-        <v>112.5571245311111</v>
+        <v>111.5080739111111</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1645494217018862</v>
+        <v>0.1675181572444334</v>
       </c>
       <c r="T61">
-        <v>1.547703048635559</v>
+        <v>1.586395624851448</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.004486165490532379</v>
+        <v>0.004411396065690174</v>
       </c>
       <c r="W61">
-        <v>0.2347421621773325</v>
+        <v>0.2347597928077103</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.02990776993688249</v>
+        <v>0.02940930710460121</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.2078631385823995</v>
+        <v>0.2097631385823995</v>
       </c>
       <c r="C62">
-        <v>-58.49133338020067</v>
+        <v>-65.93263957298495</v>
       </c>
       <c r="D62">
-        <v>249.3286666197993</v>
+        <v>247.121360427015</v>
       </c>
       <c r="E62">
-        <v>179.54</v>
+        <v>184.774</v>
       </c>
       <c r="F62">
-        <v>314.04</v>
+        <v>319.274</v>
       </c>
       <c r="G62">
         <v>6.22</v>
@@ -6371,37 +6371,37 @@
         <v>2.177777777777806</v>
       </c>
       <c r="M62">
-        <v>74.05063199999999</v>
+        <v>75.2848092</v>
       </c>
       <c r="N62">
-        <v>-71.87285422222219</v>
+        <v>-73.10703142222219</v>
       </c>
       <c r="O62">
-        <v>-10.78092813333333</v>
+        <v>-10.96605471333333</v>
       </c>
       <c r="P62">
-        <v>-61.09192608888886</v>
+        <v>-62.14097670888886</v>
       </c>
       <c r="Q62">
-        <v>111.5080739111111</v>
+        <v>110.4590232911111</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1675181572444334</v>
+        <v>0.1706391356353163</v>
       </c>
       <c r="T62">
-        <v>1.586395624851448</v>
+        <v>1.627072435745075</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.004411396065690174</v>
+        <v>0.00433907809740017</v>
       </c>
       <c r="W62">
-        <v>0.2347597928077103</v>
+        <v>0.234776845384633</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.02940930710460121</v>
+        <v>0.02892718731600119</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.2097631385823995</v>
+        <v>0.2116631385823995</v>
       </c>
       <c r="C63">
-        <v>-65.93263957298495</v>
+        <v>-73.33520617258719</v>
       </c>
       <c r="D63">
-        <v>247.121360427015</v>
+        <v>244.9527938274128</v>
       </c>
       <c r="E63">
-        <v>184.774</v>
+        <v>190.008</v>
       </c>
       <c r="F63">
-        <v>319.274</v>
+        <v>324.508</v>
       </c>
       <c r="G63">
         <v>6.22</v>
@@ -6453,37 +6453,37 @@
         <v>2.177777777777806</v>
       </c>
       <c r="M63">
-        <v>75.2848092</v>
+        <v>76.5189864</v>
       </c>
       <c r="N63">
-        <v>-73.10703142222219</v>
+        <v>-74.3412086222222</v>
       </c>
       <c r="O63">
-        <v>-10.96605471333333</v>
+        <v>-11.15118129333333</v>
       </c>
       <c r="P63">
-        <v>-62.14097670888886</v>
+        <v>-63.19002732888887</v>
       </c>
       <c r="Q63">
-        <v>110.4590232911111</v>
+        <v>109.4099726711111</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1706391356353163</v>
+        <v>0.173924376046772</v>
       </c>
       <c r="T63">
-        <v>1.627072435745075</v>
+        <v>1.669890131422577</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.00433907809740017</v>
+        <v>0.004269092966796941</v>
       </c>
       <c r="W63">
-        <v>0.234776845384633</v>
+        <v>0.2347933478784293</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.02892718731600119</v>
+        <v>0.02846061977864622</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.2116631385823995</v>
+        <v>0.2135631385823995</v>
       </c>
       <c r="C64">
-        <v>-73.33520617258719</v>
+        <v>-80.70004416315163</v>
       </c>
       <c r="D64">
-        <v>244.9527938274128</v>
+        <v>242.8219558368483</v>
       </c>
       <c r="E64">
-        <v>190.008</v>
+        <v>195.242</v>
       </c>
       <c r="F64">
-        <v>324.508</v>
+        <v>329.742</v>
       </c>
       <c r="G64">
         <v>6.22</v>
@@ -6535,37 +6535,37 @@
         <v>2.177777777777806</v>
       </c>
       <c r="M64">
-        <v>76.5189864</v>
+        <v>77.75316359999999</v>
       </c>
       <c r="N64">
-        <v>-74.3412086222222</v>
+        <v>-75.57538582222219</v>
       </c>
       <c r="O64">
-        <v>-11.15118129333333</v>
+        <v>-11.33630787333333</v>
       </c>
       <c r="P64">
-        <v>-63.19002732888887</v>
+        <v>-64.23907794888886</v>
       </c>
       <c r="Q64">
-        <v>109.4099726711111</v>
+        <v>108.3609220511111</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.173924376046772</v>
+        <v>0.177387197021009</v>
       </c>
       <c r="T64">
-        <v>1.669890131422577</v>
+        <v>1.7150222971367</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.004269092966796941</v>
+        <v>0.004201329586371594</v>
       </c>
       <c r="W64">
-        <v>0.2347933478784293</v>
+        <v>0.2348093264835336</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.02846061977864622</v>
+        <v>0.02800886390914392</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.2135631385823995</v>
+        <v>0.2154631385823995</v>
       </c>
       <c r="C65">
-        <v>-80.70004416315163</v>
+        <v>-88.02812965409791</v>
       </c>
       <c r="D65">
-        <v>242.8219558368483</v>
+        <v>240.7278703459021</v>
       </c>
       <c r="E65">
-        <v>195.242</v>
+        <v>200.476</v>
       </c>
       <c r="F65">
-        <v>329.742</v>
+        <v>334.976</v>
       </c>
       <c r="G65">
         <v>6.22</v>
@@ -6617,37 +6617,37 @@
         <v>2.177777777777806</v>
       </c>
       <c r="M65">
-        <v>77.75316359999999</v>
+        <v>78.9873408</v>
       </c>
       <c r="N65">
-        <v>-75.57538582222219</v>
+        <v>-76.80956302222219</v>
       </c>
       <c r="O65">
-        <v>-11.33630787333333</v>
+        <v>-11.52143445333333</v>
       </c>
       <c r="P65">
-        <v>-64.23907794888886</v>
+        <v>-65.28812856888887</v>
       </c>
       <c r="Q65">
-        <v>108.3609220511111</v>
+        <v>107.3118714311111</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.177387197021009</v>
+        <v>0.1810423969382593</v>
       </c>
       <c r="T65">
-        <v>1.7150222971367</v>
+        <v>1.762661805390498</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.004201329586371594</v>
+        <v>0.004135683811584537</v>
       </c>
       <c r="W65">
-        <v>0.2348093264835336</v>
+        <v>0.2348248057572284</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.02800886390914392</v>
+        <v>0.02757122541056356</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.2154631385823995</v>
+        <v>0.2173631385823995</v>
       </c>
       <c r="C66">
-        <v>-88.02812965409791</v>
+        <v>-95.32040537105294</v>
       </c>
       <c r="D66">
-        <v>240.7278703459021</v>
+        <v>238.669594628947</v>
       </c>
       <c r="E66">
-        <v>200.476</v>
+        <v>205.71</v>
       </c>
       <c r="F66">
-        <v>334.976</v>
+        <v>340.21</v>
       </c>
       <c r="G66">
         <v>6.22</v>
@@ -6699,37 +6699,37 @@
         <v>2.177777777777806</v>
       </c>
       <c r="M66">
-        <v>78.9873408</v>
+        <v>80.221518</v>
       </c>
       <c r="N66">
-        <v>-76.80956302222219</v>
+        <v>-78.0437402222222</v>
       </c>
       <c r="O66">
-        <v>-11.52143445333333</v>
+        <v>-11.70656103333333</v>
       </c>
       <c r="P66">
-        <v>-65.28812856888887</v>
+        <v>-66.33717918888887</v>
       </c>
       <c r="Q66">
-        <v>107.3118714311111</v>
+        <v>106.2628208111111</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1810423969382593</v>
+        <v>0.1849064654222096</v>
       </c>
       <c r="T66">
-        <v>1.762661805390498</v>
+        <v>1.813023571258798</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.004135683811584537</v>
+        <v>0.004072057906790928</v>
       </c>
       <c r="W66">
-        <v>0.2348248057572284</v>
+        <v>0.2348398087455787</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.02757122541056356</v>
+        <v>0.02714705271193951</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.2173631385823995</v>
+        <v>0.2192631385823995</v>
       </c>
       <c r="C67">
-        <v>-95.32040537105294</v>
+        <v>-102.5777820709454</v>
       </c>
       <c r="D67">
-        <v>238.669594628947</v>
+        <v>236.6462179290546</v>
       </c>
       <c r="E67">
-        <v>205.71</v>
+        <v>210.944</v>
       </c>
       <c r="F67">
-        <v>340.21</v>
+        <v>345.444</v>
       </c>
       <c r="G67">
         <v>6.22</v>
@@ -6781,37 +6781,37 @@
         <v>2.177777777777806</v>
       </c>
       <c r="M67">
-        <v>80.221518</v>
+        <v>81.45569520000001</v>
       </c>
       <c r="N67">
-        <v>-78.0437402222222</v>
+        <v>-79.2779174222222</v>
       </c>
       <c r="O67">
-        <v>-11.70656103333333</v>
+        <v>-11.89168761333333</v>
       </c>
       <c r="P67">
-        <v>-66.33717918888887</v>
+        <v>-67.38622980888887</v>
       </c>
       <c r="Q67">
-        <v>106.2628208111111</v>
+        <v>105.2137701911111</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1849064654222096</v>
+        <v>0.1889978320522746</v>
       </c>
       <c r="T67">
-        <v>1.813023571258798</v>
+        <v>1.86634779394288</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.004072057906790928</v>
+        <v>0.004010360059718339</v>
       </c>
       <c r="W67">
-        <v>0.2348398087455787</v>
+        <v>0.2348543570979184</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.02714705271193951</v>
+        <v>0.02673573373145555</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.2192631385823995</v>
+        <v>0.2211631385823995</v>
       </c>
       <c r="C68">
-        <v>-102.5777820709454</v>
+        <v>-109.8011398857239</v>
       </c>
       <c r="D68">
-        <v>236.6462179290546</v>
+        <v>234.6568601142761</v>
       </c>
       <c r="E68">
-        <v>210.944</v>
+        <v>216.178</v>
       </c>
       <c r="F68">
-        <v>345.444</v>
+        <v>350.678</v>
       </c>
       <c r="G68">
         <v>6.22</v>
@@ -6863,37 +6863,37 @@
         <v>2.177777777777806</v>
       </c>
       <c r="M68">
-        <v>81.45569520000001</v>
+        <v>82.6898724</v>
       </c>
       <c r="N68">
-        <v>-79.2779174222222</v>
+        <v>-80.51209462222219</v>
       </c>
       <c r="O68">
-        <v>-11.89168761333333</v>
+        <v>-12.07681419333333</v>
       </c>
       <c r="P68">
-        <v>-67.38622980888887</v>
+        <v>-68.43528042888886</v>
       </c>
       <c r="Q68">
-        <v>105.2137701911111</v>
+        <v>104.1647195711111</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1889978320522746</v>
+        <v>0.1933371602962829</v>
       </c>
       <c r="T68">
-        <v>1.86634779394288</v>
+        <v>1.922903787698725</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.004010360059718339</v>
+        <v>0.003950503939424035</v>
       </c>
       <c r="W68">
-        <v>0.2348543570979184</v>
+        <v>0.2348684711710838</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.02673573373145555</v>
+        <v>0.02633669292949359</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.2211631385823995</v>
+        <v>0.2230631385823995</v>
       </c>
       <c r="C69">
-        <v>-109.8011398857239</v>
+        <v>-116.9913295988657</v>
       </c>
       <c r="D69">
-        <v>234.6568601142761</v>
+        <v>232.7006704011343</v>
       </c>
       <c r="E69">
-        <v>216.178</v>
+        <v>221.412</v>
       </c>
       <c r="F69">
-        <v>350.678</v>
+        <v>355.912</v>
       </c>
       <c r="G69">
         <v>6.22</v>
@@ -6945,37 +6945,37 @@
         <v>2.177777777777806</v>
       </c>
       <c r="M69">
-        <v>82.6898724</v>
+        <v>83.92404960000002</v>
       </c>
       <c r="N69">
-        <v>-80.51209462222219</v>
+        <v>-81.74627182222221</v>
       </c>
       <c r="O69">
-        <v>-12.07681419333333</v>
+        <v>-12.26194077333333</v>
       </c>
       <c r="P69">
-        <v>-68.43528042888886</v>
+        <v>-69.48433104888888</v>
       </c>
       <c r="Q69">
-        <v>104.1647195711111</v>
+        <v>103.1156689511111</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1933371602962829</v>
+        <v>0.1979476965555417</v>
       </c>
       <c r="T69">
-        <v>1.922903787698725</v>
+        <v>1.98299453106431</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.003950503939424035</v>
+        <v>0.003892408293256034</v>
       </c>
       <c r="W69">
-        <v>0.2348684711710838</v>
+        <v>0.2348821701244503</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.02633669292949359</v>
+        <v>0.02594938862170693</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2230631385823995</v>
+        <v>0.2249631385823995</v>
       </c>
       <c r="C70">
-        <v>-116.9913295988657</v>
+        <v>-124.1491738585627</v>
       </c>
       <c r="D70">
-        <v>232.7006704011343</v>
+        <v>230.7768261414373</v>
       </c>
       <c r="E70">
-        <v>221.412</v>
+        <v>226.646</v>
       </c>
       <c r="F70">
-        <v>355.912</v>
+        <v>361.146</v>
       </c>
       <c r="G70">
         <v>6.22</v>
@@ -7027,37 +7027,37 @@
         <v>2.177777777777806</v>
       </c>
       <c r="M70">
-        <v>83.92404960000002</v>
+        <v>85.15822680000001</v>
       </c>
       <c r="N70">
-        <v>-81.74627182222221</v>
+        <v>-82.9804490222222</v>
       </c>
       <c r="O70">
-        <v>-12.26194077333333</v>
+        <v>-12.44706735333333</v>
       </c>
       <c r="P70">
-        <v>-69.48433104888888</v>
+        <v>-70.53338166888888</v>
       </c>
       <c r="Q70">
-        <v>103.1156689511111</v>
+        <v>102.0666183311111</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1979476965555417</v>
+        <v>0.2028556867670109</v>
       </c>
       <c r="T70">
-        <v>1.98299453106431</v>
+        <v>2.046962096582514</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.003892408293256034</v>
+        <v>0.003835996578861019</v>
       </c>
       <c r="W70">
-        <v>0.2348821701244503</v>
+        <v>0.2348954720067046</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.02594938862170693</v>
+        <v>0.02557331052574008</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2249631385823995</v>
+        <v>0.2268631385823995</v>
       </c>
       <c r="C71">
-        <v>-124.1491738585627</v>
+        <v>-131.275468331223</v>
       </c>
       <c r="D71">
-        <v>230.7768261414373</v>
+        <v>228.884531668777</v>
       </c>
       <c r="E71">
-        <v>226.646</v>
+        <v>231.88</v>
       </c>
       <c r="F71">
-        <v>361.146</v>
+        <v>366.38</v>
       </c>
       <c r="G71">
         <v>6.22</v>
@@ -7109,37 +7109,37 @@
         <v>2.177777777777806</v>
       </c>
       <c r="M71">
-        <v>85.15822680000001</v>
+        <v>86.392404</v>
       </c>
       <c r="N71">
-        <v>-82.9804490222222</v>
+        <v>-84.21462622222219</v>
       </c>
       <c r="O71">
-        <v>-12.44706735333333</v>
+        <v>-12.63219393333333</v>
       </c>
       <c r="P71">
-        <v>-70.53338166888888</v>
+        <v>-71.58243228888887</v>
       </c>
       <c r="Q71">
-        <v>102.0666183311111</v>
+        <v>101.0175677111111</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2028556867670109</v>
+        <v>0.2080908763259112</v>
       </c>
       <c r="T71">
-        <v>2.046962096582514</v>
+        <v>2.115194166468598</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.003835996578861019</v>
+        <v>0.003781196627734434</v>
       </c>
       <c r="W71">
-        <v>0.2348954720067046</v>
+        <v>0.2349083938351802</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.02557331052574008</v>
+        <v>0.02520797751822956</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2268631385823995</v>
+        <v>0.2287631385823996</v>
       </c>
       <c r="C72">
-        <v>-131.275468331223</v>
+        <v>-138.3709827986828</v>
       </c>
       <c r="D72">
-        <v>228.884531668777</v>
+        <v>227.0230172013172</v>
       </c>
       <c r="E72">
-        <v>231.88</v>
+        <v>237.114</v>
       </c>
       <c r="F72">
-        <v>366.38</v>
+        <v>371.614</v>
       </c>
       <c r="G72">
         <v>6.22</v>
@@ -7191,37 +7191,37 @@
         <v>2.177777777777806</v>
       </c>
       <c r="M72">
-        <v>86.392404</v>
+        <v>87.62658120000002</v>
       </c>
       <c r="N72">
-        <v>-84.21462622222219</v>
+        <v>-85.44880342222221</v>
       </c>
       <c r="O72">
-        <v>-12.63219393333333</v>
+        <v>-12.81732051333333</v>
       </c>
       <c r="P72">
-        <v>-71.58243228888887</v>
+        <v>-72.63148290888888</v>
       </c>
       <c r="Q72">
-        <v>101.0175677111111</v>
+        <v>99.96851709111111</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2080908763259112</v>
+        <v>0.2136871134405978</v>
       </c>
       <c r="T72">
-        <v>2.115194166468598</v>
+        <v>2.188131896346826</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.003781196627734434</v>
+        <v>0.003727940337202963</v>
       </c>
       <c r="W72">
-        <v>0.2349083938351802</v>
+        <v>0.2349209516684876</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.02520797751822956</v>
+        <v>0.02485293558135304</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2287631385823995</v>
+        <v>0.2306631385823995</v>
       </c>
       <c r="C73">
-        <v>-138.3709827986828</v>
+        <v>-145.4364622023085</v>
       </c>
       <c r="D73">
-        <v>227.0230172013172</v>
+        <v>225.1915377976914</v>
       </c>
       <c r="E73">
-        <v>237.114</v>
+        <v>242.348</v>
       </c>
       <c r="F73">
-        <v>371.614</v>
+        <v>376.848</v>
       </c>
       <c r="G73">
         <v>6.22</v>
@@ -7273,37 +7273,37 @@
         <v>2.177777777777806</v>
       </c>
       <c r="M73">
-        <v>87.6265812</v>
+        <v>88.86075839999999</v>
       </c>
       <c r="N73">
-        <v>-85.4488034222222</v>
+        <v>-86.68298062222219</v>
       </c>
       <c r="O73">
-        <v>-12.81732051333333</v>
+        <v>-13.00244709333333</v>
       </c>
       <c r="P73">
-        <v>-72.63148290888887</v>
+        <v>-73.68053352888886</v>
       </c>
       <c r="Q73">
-        <v>99.96851709111112</v>
+        <v>98.91946647111114</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2136871134405978</v>
+        <v>0.219683081777762</v>
       </c>
       <c r="T73">
-        <v>2.188131896346825</v>
+        <v>2.266279464073497</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.003727940337202963</v>
+        <v>0.003676163388075144</v>
       </c>
       <c r="W73">
-        <v>0.2349209516684876</v>
+        <v>0.2349331606730919</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.02485293558135304</v>
+        <v>0.02450775592050092</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2306631385823995</v>
+        <v>0.2325631385823995</v>
       </c>
       <c r="C74">
-        <v>-145.4364622023085</v>
+        <v>-152.4726276369657</v>
       </c>
       <c r="D74">
-        <v>225.1915377976914</v>
+        <v>223.3893723630343</v>
       </c>
       <c r="E74">
-        <v>242.348</v>
+        <v>247.582</v>
       </c>
       <c r="F74">
-        <v>376.848</v>
+        <v>382.082</v>
       </c>
       <c r="G74">
         <v>6.22</v>
@@ -7355,37 +7355,37 @@
         <v>2.177777777777806</v>
       </c>
       <c r="M74">
-        <v>88.86075839999999</v>
+        <v>90.0949356</v>
       </c>
       <c r="N74">
-        <v>-86.68298062222219</v>
+        <v>-87.91715782222219</v>
       </c>
       <c r="O74">
-        <v>-13.00244709333333</v>
+        <v>-13.18757367333333</v>
       </c>
       <c r="P74">
-        <v>-73.68053352888886</v>
+        <v>-74.72958414888886</v>
       </c>
       <c r="Q74">
-        <v>98.91946647111114</v>
+        <v>97.87041585111113</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.219683081777762</v>
+        <v>0.226123195917679</v>
       </c>
       <c r="T74">
-        <v>2.266279464073497</v>
+        <v>2.350215740520663</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.003676163388075144</v>
+        <v>0.003625804985498772</v>
       </c>
       <c r="W74">
-        <v>0.2349331606730919</v>
+        <v>0.2349450351844194</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.02450775592050092</v>
+        <v>0.02417203323665851</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2325631385823995</v>
+        <v>0.2344631385823995</v>
       </c>
       <c r="C75">
-        <v>-152.4726276369657</v>
+        <v>-159.4801772976378</v>
       </c>
       <c r="D75">
-        <v>223.3893723630343</v>
+        <v>221.6158227023622</v>
       </c>
       <c r="E75">
-        <v>247.582</v>
+        <v>252.816</v>
       </c>
       <c r="F75">
-        <v>382.082</v>
+        <v>387.316</v>
       </c>
       <c r="G75">
         <v>6.22</v>
@@ -7437,37 +7437,37 @@
         <v>2.177777777777806</v>
       </c>
       <c r="M75">
-        <v>90.0949356</v>
+        <v>91.3291128</v>
       </c>
       <c r="N75">
-        <v>-87.91715782222219</v>
+        <v>-89.1513350222222</v>
       </c>
       <c r="O75">
-        <v>-13.18757367333333</v>
+        <v>-13.37270025333333</v>
       </c>
       <c r="P75">
-        <v>-74.72958414888886</v>
+        <v>-75.77863476888886</v>
       </c>
       <c r="Q75">
-        <v>97.87041585111113</v>
+        <v>96.82136523111113</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.226123195917679</v>
+        <v>0.2330587034529744</v>
       </c>
       <c r="T75">
-        <v>2.350215740520663</v>
+        <v>2.440608653617612</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.003625804985498772</v>
+        <v>0.00357680762082987</v>
       </c>
       <c r="W75">
-        <v>0.2349450351844194</v>
+        <v>0.2349565887630083</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.02417203323665851</v>
+        <v>0.02384538413886583</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2344631385823995</v>
+        <v>0.2363631385823995</v>
       </c>
       <c r="C76">
-        <v>-159.4801772976378</v>
+        <v>-166.4597873813084</v>
       </c>
       <c r="D76">
-        <v>221.6158227023622</v>
+        <v>219.8702126186916</v>
       </c>
       <c r="E76">
-        <v>252.816</v>
+        <v>258.05</v>
       </c>
       <c r="F76">
-        <v>387.316</v>
+        <v>392.55</v>
       </c>
       <c r="G76">
         <v>6.22</v>
@@ -7519,37 +7519,37 @@
         <v>2.177777777777806</v>
       </c>
       <c r="M76">
-        <v>91.3291128</v>
+        <v>92.56328999999999</v>
       </c>
       <c r="N76">
-        <v>-89.1513350222222</v>
+        <v>-90.38551222222219</v>
       </c>
       <c r="O76">
-        <v>-13.37270025333333</v>
+        <v>-13.55782683333333</v>
       </c>
       <c r="P76">
-        <v>-75.77863476888886</v>
+        <v>-76.82768538888887</v>
       </c>
       <c r="Q76">
-        <v>96.82136523111113</v>
+        <v>95.77231461111113</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2330587034529744</v>
+        <v>0.2405490515910934</v>
       </c>
       <c r="T76">
-        <v>2.440608653617612</v>
+        <v>2.538232999762317</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.00357680762082987</v>
+        <v>0.003529116852552139</v>
       </c>
       <c r="W76">
-        <v>0.2349565887630083</v>
+        <v>0.2349678342461682</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.02384538413886583</v>
+        <v>0.02352744568368093</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2363631385823995</v>
+        <v>0.2382631385823995</v>
       </c>
       <c r="C77">
-        <v>-166.4597873813084</v>
+        <v>-173.4121129465535</v>
       </c>
       <c r="D77">
-        <v>219.8702126186916</v>
+        <v>218.1518870534465</v>
       </c>
       <c r="E77">
-        <v>258.05</v>
+        <v>263.284</v>
       </c>
       <c r="F77">
-        <v>392.55</v>
+        <v>397.784</v>
       </c>
       <c r="G77">
         <v>6.22</v>
@@ -7601,37 +7601,37 @@
         <v>2.177777777777806</v>
       </c>
       <c r="M77">
-        <v>92.56328999999999</v>
+        <v>93.7974672</v>
       </c>
       <c r="N77">
-        <v>-90.38551222222219</v>
+        <v>-91.61968942222219</v>
       </c>
       <c r="O77">
-        <v>-13.55782683333333</v>
+        <v>-13.74295341333333</v>
       </c>
       <c r="P77">
-        <v>-76.82768538888887</v>
+        <v>-77.87673600888887</v>
       </c>
       <c r="Q77">
-        <v>95.77231461111113</v>
+        <v>94.72326399111112</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2405490515910934</v>
+        <v>0.248663595407389</v>
       </c>
       <c r="T77">
-        <v>2.538232999762317</v>
+        <v>2.643992708085747</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.003529116852552139</v>
+        <v>0.003482681104492242</v>
       </c>
       <c r="W77">
-        <v>0.2349678342461682</v>
+        <v>0.2349787837955608</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.02352744568368093</v>
+        <v>0.02321787402994824</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2382631385823995</v>
+        <v>0.2401631385823995</v>
       </c>
       <c r="C78">
-        <v>-173.4121129465535</v>
+        <v>-180.3377887331378</v>
       </c>
       <c r="D78">
-        <v>218.1518870534465</v>
+        <v>216.4602112668622</v>
       </c>
       <c r="E78">
-        <v>263.284</v>
+        <v>268.518</v>
       </c>
       <c r="F78">
-        <v>397.784</v>
+        <v>403.018</v>
       </c>
       <c r="G78">
         <v>6.22</v>
@@ -7683,37 +7683,37 @@
         <v>2.177777777777806</v>
       </c>
       <c r="M78">
-        <v>93.7974672</v>
+        <v>95.03164439999999</v>
       </c>
       <c r="N78">
-        <v>-91.61968942222219</v>
+        <v>-92.85386662222218</v>
       </c>
       <c r="O78">
-        <v>-13.74295341333333</v>
+        <v>-13.92807999333333</v>
       </c>
       <c r="P78">
-        <v>-77.87673600888887</v>
+        <v>-78.92578662888886</v>
       </c>
       <c r="Q78">
-        <v>94.72326399111112</v>
+        <v>93.67421337111114</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.248663595407389</v>
+        <v>0.2574837517294493</v>
       </c>
       <c r="T78">
-        <v>2.643992708085747</v>
+        <v>2.758948912785127</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.003482681104492242</v>
+        <v>0.003437451479758576</v>
       </c>
       <c r="W78">
-        <v>0.2349787837955608</v>
+        <v>0.2349894489410729</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.02321787402994824</v>
+        <v>0.02291634319839053</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2401631385823995</v>
+        <v>0.2420631385823995</v>
       </c>
       <c r="C79">
-        <v>-180.3377887331378</v>
+        <v>-187.2374299437723</v>
       </c>
       <c r="D79">
-        <v>216.4602112668622</v>
+        <v>214.7945700562277</v>
       </c>
       <c r="E79">
-        <v>268.518</v>
+        <v>273.752</v>
       </c>
       <c r="F79">
-        <v>403.018</v>
+        <v>408.252</v>
       </c>
       <c r="G79">
         <v>6.22</v>
@@ -7765,37 +7765,37 @@
         <v>2.177777777777806</v>
       </c>
       <c r="M79">
-        <v>95.03164439999999</v>
+        <v>96.26582160000001</v>
       </c>
       <c r="N79">
-        <v>-92.85386662222218</v>
+        <v>-94.0880438222222</v>
       </c>
       <c r="O79">
-        <v>-13.92807999333333</v>
+        <v>-14.11320657333333</v>
       </c>
       <c r="P79">
-        <v>-78.92578662888886</v>
+        <v>-79.97483724888887</v>
       </c>
       <c r="Q79">
-        <v>93.67421337111114</v>
+        <v>92.62516275111112</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2574837517294493</v>
+        <v>0.2671057404444243</v>
       </c>
       <c r="T79">
-        <v>2.758948912785127</v>
+        <v>2.884355681548088</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.003437451479758576</v>
+        <v>0.003393381588992441</v>
       </c>
       <c r="W79">
-        <v>0.2349894489410729</v>
+        <v>0.2349998406213156</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.02291634319839053</v>
+        <v>0.02262254392661622</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2420631385823995</v>
+        <v>0.2439631385823995</v>
       </c>
       <c r="C80">
-        <v>-187.2374299437723</v>
+        <v>-194.1116329900531</v>
       </c>
       <c r="D80">
-        <v>214.7945700562277</v>
+        <v>213.1543670099469</v>
       </c>
       <c r="E80">
-        <v>273.752</v>
+        <v>278.986</v>
       </c>
       <c r="F80">
-        <v>408.252</v>
+        <v>413.486</v>
       </c>
       <c r="G80">
         <v>6.22</v>
@@ -7847,37 +7847,37 @@
         <v>2.177777777777806</v>
       </c>
       <c r="M80">
-        <v>96.26582160000001</v>
+        <v>97.4999988</v>
       </c>
       <c r="N80">
-        <v>-94.0880438222222</v>
+        <v>-95.32222102222219</v>
       </c>
       <c r="O80">
-        <v>-14.11320657333333</v>
+        <v>-14.29833315333333</v>
       </c>
       <c r="P80">
-        <v>-79.97483724888887</v>
+        <v>-81.02388786888886</v>
       </c>
       <c r="Q80">
-        <v>92.62516275111112</v>
+        <v>91.57611213111113</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2671057404444243</v>
+        <v>0.277644109037016</v>
       </c>
       <c r="T80">
-        <v>2.884355681548088</v>
+        <v>3.021705952097997</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.003393381588992441</v>
+        <v>0.003350427391663423</v>
       </c>
       <c r="W80">
-        <v>0.2349998406213156</v>
+        <v>0.2350099692210458</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.02262254392661622</v>
+        <v>0.02233618261108949</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2439631385823995</v>
+        <v>0.2458631385823995</v>
       </c>
       <c r="C81">
-        <v>-194.1116329900531</v>
+        <v>-200.9609762044828</v>
       </c>
       <c r="D81">
-        <v>213.1543670099469</v>
+        <v>211.5390237955172</v>
       </c>
       <c r="E81">
-        <v>278.986</v>
+        <v>284.22</v>
       </c>
       <c r="F81">
-        <v>413.486</v>
+        <v>418.72</v>
       </c>
       <c r="G81">
         <v>6.22</v>
@@ -7929,37 +7929,37 @@
         <v>2.177777777777806</v>
       </c>
       <c r="M81">
-        <v>97.4999988</v>
+        <v>98.73417600000001</v>
       </c>
       <c r="N81">
-        <v>-95.32222102222219</v>
+        <v>-96.5563982222222</v>
       </c>
       <c r="O81">
-        <v>-14.29833315333333</v>
+        <v>-14.48345973333333</v>
       </c>
       <c r="P81">
-        <v>-81.02388786888886</v>
+        <v>-82.07293848888887</v>
       </c>
       <c r="Q81">
-        <v>91.57611213111113</v>
+        <v>90.52706151111113</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.277644109037016</v>
+        <v>0.2892363144888668</v>
       </c>
       <c r="T81">
-        <v>3.021705952097997</v>
+        <v>3.172791249702897</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.003350427391663423</v>
+        <v>0.00330854704926763</v>
       </c>
       <c r="W81">
-        <v>0.2350099692210458</v>
+        <v>0.2350198446057827</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.02233618261108949</v>
+        <v>0.02205698032845083</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2458631385823995</v>
+        <v>0.2477631385823995</v>
       </c>
       <c r="C82">
-        <v>-200.9609762044828</v>
+        <v>-207.7860205203604</v>
       </c>
       <c r="D82">
-        <v>211.5390237955172</v>
+        <v>209.9479794796397</v>
       </c>
       <c r="E82">
-        <v>284.22</v>
+        <v>289.454</v>
       </c>
       <c r="F82">
-        <v>418.72</v>
+        <v>423.954</v>
       </c>
       <c r="G82">
         <v>6.22</v>
@@ -8011,37 +8011,37 @@
         <v>2.177777777777806</v>
       </c>
       <c r="M82">
-        <v>98.73417600000001</v>
+        <v>99.96835320000001</v>
       </c>
       <c r="N82">
-        <v>-96.5563982222222</v>
+        <v>-97.7905754222222</v>
       </c>
       <c r="O82">
-        <v>-14.48345973333333</v>
+        <v>-14.66858631333333</v>
       </c>
       <c r="P82">
-        <v>-82.07293848888887</v>
+        <v>-83.12198910888887</v>
       </c>
       <c r="Q82">
-        <v>90.52706151111113</v>
+        <v>89.47801089111113</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2892363144888668</v>
+        <v>0.302048752093544</v>
       </c>
       <c r="T82">
-        <v>3.172791249702897</v>
+        <v>3.339780262845155</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.00330854704926763</v>
+        <v>0.003267700789400127</v>
       </c>
       <c r="W82">
-        <v>0.2350198446057827</v>
+        <v>0.2350294761538595</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.02205698032845083</v>
+        <v>0.0217846719293342</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2477631385823995</v>
+        <v>0.2496631385823995</v>
       </c>
       <c r="C83">
-        <v>-207.7860205203604</v>
+        <v>-214.5873101212179</v>
       </c>
       <c r="D83">
-        <v>209.9479794796397</v>
+        <v>208.3806898787821</v>
       </c>
       <c r="E83">
-        <v>289.454</v>
+        <v>294.688</v>
       </c>
       <c r="F83">
-        <v>423.954</v>
+        <v>429.188</v>
       </c>
       <c r="G83">
         <v>6.22</v>
@@ -8093,37 +8093,37 @@
         <v>2.177777777777806</v>
       </c>
       <c r="M83">
-        <v>99.96835320000001</v>
+        <v>101.2025304</v>
       </c>
       <c r="N83">
-        <v>-97.7905754222222</v>
+        <v>-99.02475262222219</v>
       </c>
       <c r="O83">
-        <v>-14.66858631333333</v>
+        <v>-14.85371289333333</v>
       </c>
       <c r="P83">
-        <v>-83.12198910888887</v>
+        <v>-84.17103972888887</v>
       </c>
       <c r="Q83">
-        <v>89.47801089111113</v>
+        <v>88.42896027111112</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.302048752093544</v>
+        <v>0.3162847938765187</v>
       </c>
       <c r="T83">
-        <v>3.339780262845155</v>
+        <v>3.525323610780997</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.003267700789400127</v>
+        <v>0.003227850779773298</v>
       </c>
       <c r="W83">
-        <v>0.2350294761538595</v>
+        <v>0.2350388727861295</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.0217846719293342</v>
+        <v>0.02151900519848859</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2496631385823995</v>
+        <v>0.2515631385823995</v>
       </c>
       <c r="C84">
-        <v>-214.5873101212179</v>
+        <v>-221.3653730613845</v>
       </c>
       <c r="D84">
-        <v>208.3806898787821</v>
+        <v>206.8366269386155</v>
       </c>
       <c r="E84">
-        <v>294.688</v>
+        <v>299.922</v>
       </c>
       <c r="F84">
-        <v>429.188</v>
+        <v>434.422</v>
       </c>
       <c r="G84">
         <v>6.22</v>
@@ -8175,37 +8175,37 @@
         <v>2.177777777777806</v>
       </c>
       <c r="M84">
-        <v>101.2025304</v>
+        <v>102.4367076</v>
       </c>
       <c r="N84">
-        <v>-99.02475262222219</v>
+        <v>-100.2589298222222</v>
       </c>
       <c r="O84">
-        <v>-14.85371289333333</v>
+        <v>-15.03883947333333</v>
       </c>
       <c r="P84">
-        <v>-84.17103972888887</v>
+        <v>-85.22009034888887</v>
       </c>
       <c r="Q84">
-        <v>88.42896027111112</v>
+        <v>87.37990965111112</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3162847938765187</v>
+        <v>0.3321956641045493</v>
       </c>
       <c r="T84">
-        <v>3.525323610780997</v>
+        <v>3.732695587885762</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.003227850779773298</v>
+        <v>0.003188961011342294</v>
       </c>
       <c r="W84">
-        <v>0.2350388727861295</v>
+        <v>0.2350480429935255</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.02151900519848859</v>
+        <v>0.02125974007561526</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2515631385823995</v>
+        <v>0.2534631385823995</v>
       </c>
       <c r="C85">
-        <v>-221.3653730613845</v>
+        <v>-228.1207218591626</v>
       </c>
       <c r="D85">
-        <v>206.8366269386155</v>
+        <v>205.3152781408374</v>
       </c>
       <c r="E85">
-        <v>299.922</v>
+        <v>305.156</v>
       </c>
       <c r="F85">
-        <v>434.422</v>
+        <v>439.656</v>
       </c>
       <c r="G85">
         <v>6.22</v>
@@ -8257,37 +8257,37 @@
         <v>2.177777777777806</v>
       </c>
       <c r="M85">
-        <v>102.4367076</v>
+        <v>103.6708848</v>
       </c>
       <c r="N85">
-        <v>-100.2589298222222</v>
+        <v>-101.4931070222222</v>
       </c>
       <c r="O85">
-        <v>-15.03883947333333</v>
+        <v>-15.22396605333333</v>
       </c>
       <c r="P85">
-        <v>-85.22009034888887</v>
+        <v>-86.26914096888888</v>
       </c>
       <c r="Q85">
-        <v>87.37990965111112</v>
+        <v>86.33085903111112</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3321956641045493</v>
+        <v>0.3500953931110836</v>
       </c>
       <c r="T85">
-        <v>3.732695587885762</v>
+        <v>3.965989062128622</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.003188961011342294</v>
+        <v>0.003150997189778695</v>
       </c>
       <c r="W85">
-        <v>0.2350480429935255</v>
+        <v>0.2350569948626502</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.02125974007561526</v>
+        <v>0.02100664793185791</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2534631385823995</v>
+        <v>0.2553631385823995</v>
       </c>
       <c r="C86">
-        <v>-228.1207218591625</v>
+        <v>-234.8538540640185</v>
       </c>
       <c r="D86">
-        <v>205.3152781408374</v>
+        <v>203.8161459359815</v>
       </c>
       <c r="E86">
-        <v>305.1559999999999</v>
+        <v>310.39</v>
       </c>
       <c r="F86">
-        <v>439.6559999999999</v>
+        <v>444.89</v>
       </c>
       <c r="G86">
         <v>6.22</v>
@@ -8339,37 +8339,37 @@
         <v>2.177777777777806</v>
       </c>
       <c r="M86">
-        <v>103.6708848</v>
+        <v>104.905062</v>
       </c>
       <c r="N86">
-        <v>-101.4931070222222</v>
+        <v>-102.7272842222222</v>
       </c>
       <c r="O86">
-        <v>-15.22396605333333</v>
+        <v>-15.40909263333333</v>
       </c>
       <c r="P86">
-        <v>-86.26914096888886</v>
+        <v>-87.31819158888887</v>
       </c>
       <c r="Q86">
-        <v>86.33085903111113</v>
+        <v>85.28180841111113</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3500953931110833</v>
+        <v>0.3703817526518223</v>
       </c>
       <c r="T86">
-        <v>3.965989062128619</v>
+        <v>4.230388332937195</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.003150997189778695</v>
+        <v>0.003113926634604828</v>
       </c>
       <c r="W86">
-        <v>0.2350569948626502</v>
+        <v>0.2350657360995602</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.02100664793185791</v>
+        <v>0.0207595108973655</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2553631385823995</v>
+        <v>0.2572631385823995</v>
       </c>
       <c r="C87">
-        <v>-234.8538540640185</v>
+        <v>-241.5652527991044</v>
       </c>
       <c r="D87">
-        <v>203.8161459359815</v>
+        <v>202.3387472008955</v>
       </c>
       <c r="E87">
-        <v>310.39</v>
+        <v>315.624</v>
       </c>
       <c r="F87">
-        <v>444.89</v>
+        <v>450.124</v>
       </c>
       <c r="G87">
         <v>6.22</v>
@@ -8421,37 +8421,37 @@
         <v>2.177777777777806</v>
       </c>
       <c r="M87">
-        <v>104.905062</v>
+        <v>106.1392392</v>
       </c>
       <c r="N87">
-        <v>-102.7272842222222</v>
+        <v>-103.9614614222222</v>
       </c>
       <c r="O87">
-        <v>-15.40909263333333</v>
+        <v>-15.59421921333333</v>
       </c>
       <c r="P87">
-        <v>-87.31819158888887</v>
+        <v>-88.36724220888885</v>
       </c>
       <c r="Q87">
-        <v>85.28180841111113</v>
+        <v>84.23275779111114</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3703817526518223</v>
+        <v>0.3935661635555239</v>
       </c>
       <c r="T87">
-        <v>4.230388332937195</v>
+        <v>4.532558928146994</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.003113926634604828</v>
+        <v>0.003077718185365237</v>
       </c>
       <c r="W87">
-        <v>0.2350657360995602</v>
+        <v>0.2350742740518909</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.0207595108973655</v>
+        <v>0.02051812123576824</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2572631385823995</v>
+        <v>0.2591631385823995</v>
       </c>
       <c r="C88">
-        <v>-241.5652527991044</v>
+        <v>-248.2553872803539</v>
       </c>
       <c r="D88">
-        <v>202.3387472008955</v>
+        <v>200.8826127196461</v>
       </c>
       <c r="E88">
-        <v>315.624</v>
+        <v>320.858</v>
       </c>
       <c r="F88">
-        <v>450.124</v>
+        <v>455.358</v>
       </c>
       <c r="G88">
         <v>6.22</v>
@@ -8503,37 +8503,37 @@
         <v>2.177777777777806</v>
       </c>
       <c r="M88">
-        <v>106.1392392</v>
+        <v>107.3734164</v>
       </c>
       <c r="N88">
-        <v>-103.9614614222222</v>
+        <v>-105.1956386222222</v>
       </c>
       <c r="O88">
-        <v>-15.59421921333333</v>
+        <v>-15.77934579333333</v>
       </c>
       <c r="P88">
-        <v>-88.36724220888885</v>
+        <v>-89.41629282888887</v>
       </c>
       <c r="Q88">
-        <v>84.23275779111114</v>
+        <v>83.18370717111112</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3935661635555239</v>
+        <v>0.4203174069059488</v>
       </c>
       <c r="T88">
-        <v>4.532558928146994</v>
+        <v>4.881217307235224</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.003077718185365237</v>
+        <v>0.003042342114269085</v>
       </c>
       <c r="W88">
-        <v>0.2350742740518909</v>
+        <v>0.2350826157294554</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.02051812123576824</v>
+        <v>0.02028228076179395</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2591631385823995</v>
+        <v>0.2610631385823995</v>
       </c>
       <c r="C89">
-        <v>-248.2553872803539</v>
+        <v>-254.9247133133245</v>
       </c>
       <c r="D89">
-        <v>200.8826127196461</v>
+        <v>199.4472866866755</v>
       </c>
       <c r="E89">
-        <v>320.858</v>
+        <v>326.092</v>
       </c>
       <c r="F89">
-        <v>455.358</v>
+        <v>460.592</v>
       </c>
       <c r="G89">
         <v>6.22</v>
@@ -8585,37 +8585,37 @@
         <v>2.177777777777806</v>
       </c>
       <c r="M89">
-        <v>107.3734164</v>
+        <v>108.6075936</v>
       </c>
       <c r="N89">
-        <v>-105.1956386222222</v>
+        <v>-106.4298158222222</v>
       </c>
       <c r="O89">
-        <v>-15.77934579333333</v>
+        <v>-15.96447237333333</v>
       </c>
       <c r="P89">
-        <v>-89.41629282888887</v>
+        <v>-90.46534344888886</v>
       </c>
       <c r="Q89">
-        <v>83.18370717111112</v>
+        <v>82.13465655111114</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.4203174069059488</v>
+        <v>0.4515271908147778</v>
       </c>
       <c r="T89">
-        <v>4.881217307235224</v>
+        <v>5.287985416171493</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.003042342114269085</v>
+        <v>0.003007770044788754</v>
       </c>
       <c r="W89">
-        <v>0.2350826157294554</v>
+        <v>0.2350907678234388</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.02028228076179395</v>
+        <v>0.02005180029859166</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2610631385823995</v>
+        <v>0.2629631385823995</v>
       </c>
       <c r="C90">
-        <v>-254.9247133133245</v>
+        <v>-261.5736737688914</v>
       </c>
       <c r="D90">
-        <v>199.4472866866755</v>
+        <v>198.0323262311086</v>
       </c>
       <c r="E90">
-        <v>326.092</v>
+        <v>331.326</v>
       </c>
       <c r="F90">
-        <v>460.592</v>
+        <v>465.826</v>
       </c>
       <c r="G90">
         <v>6.22</v>
@@ -8667,37 +8667,37 @@
         <v>2.177777777777806</v>
       </c>
       <c r="M90">
-        <v>108.6075936</v>
+        <v>109.8417708</v>
       </c>
       <c r="N90">
-        <v>-106.4298158222222</v>
+        <v>-107.6639930222222</v>
       </c>
       <c r="O90">
-        <v>-15.96447237333333</v>
+        <v>-16.14959895333333</v>
       </c>
       <c r="P90">
-        <v>-90.46534344888886</v>
+        <v>-91.51439406888886</v>
       </c>
       <c r="Q90">
-        <v>82.13465655111114</v>
+        <v>81.08560593111113</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.4515271908147778</v>
+        <v>0.4884114808888486</v>
       </c>
       <c r="T90">
-        <v>5.287985416171493</v>
+        <v>5.768711363096175</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.003007770044788754</v>
+        <v>0.002973974875746184</v>
       </c>
       <c r="W90">
-        <v>0.2350907678234388</v>
+        <v>0.2350987367242991</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.02005180029859166</v>
+        <v>0.01982649917164125</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2629631385823995</v>
+        <v>0.2648631385823995</v>
       </c>
       <c r="C91">
-        <v>-261.5736737688914</v>
+        <v>-268.2026990388342</v>
       </c>
       <c r="D91">
-        <v>198.0323262311086</v>
+        <v>196.6373009611658</v>
       </c>
       <c r="E91">
-        <v>331.326</v>
+        <v>336.56</v>
       </c>
       <c r="F91">
-        <v>465.826</v>
+        <v>471.06</v>
       </c>
       <c r="G91">
         <v>6.22</v>
@@ -8749,37 +8749,37 @@
         <v>2.177777777777806</v>
       </c>
       <c r="M91">
-        <v>109.8417708</v>
+        <v>111.075948</v>
       </c>
       <c r="N91">
-        <v>-107.6639930222222</v>
+        <v>-108.8981702222222</v>
       </c>
       <c r="O91">
-        <v>-16.14959895333333</v>
+        <v>-16.33472553333333</v>
       </c>
       <c r="P91">
-        <v>-91.51439406888886</v>
+        <v>-92.56344468888888</v>
       </c>
       <c r="Q91">
-        <v>81.08560593111113</v>
+        <v>80.03655531111112</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.4884114808888486</v>
+        <v>0.5326726289777336</v>
       </c>
       <c r="T91">
-        <v>5.768711363096175</v>
+        <v>6.345582499405794</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.002973974875746184</v>
+        <v>0.002940930710460115</v>
       </c>
       <c r="W91">
-        <v>0.2350987367242991</v>
+        <v>0.2351065285384735</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.01982649917164125</v>
+        <v>0.01960620473640073</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2648631385823995</v>
+        <v>0.2667631385823995</v>
       </c>
       <c r="C92">
-        <v>-268.2026990388342</v>
+        <v>-274.8122074723037</v>
       </c>
       <c r="D92">
-        <v>196.6373009611658</v>
+        <v>195.2617925276963</v>
       </c>
       <c r="E92">
-        <v>336.56</v>
+        <v>341.794</v>
       </c>
       <c r="F92">
-        <v>471.06</v>
+        <v>476.294</v>
       </c>
       <c r="G92">
         <v>6.22</v>
@@ -8831,37 +8831,37 @@
         <v>2.177777777777806</v>
       </c>
       <c r="M92">
-        <v>111.075948</v>
+        <v>112.3101252</v>
       </c>
       <c r="N92">
-        <v>-108.8981702222222</v>
+        <v>-110.1323474222222</v>
       </c>
       <c r="O92">
-        <v>-16.33472553333333</v>
+        <v>-16.51985211333333</v>
       </c>
       <c r="P92">
-        <v>-92.56344468888888</v>
+        <v>-93.61249530888887</v>
       </c>
       <c r="Q92">
-        <v>80.03655531111112</v>
+        <v>78.98750469111113</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.5326726289777336</v>
+        <v>0.5867695877530373</v>
       </c>
       <c r="T92">
-        <v>6.345582499405794</v>
+        <v>7.050647221561994</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.002940930710460115</v>
+        <v>0.00290861279056495</v>
       </c>
       <c r="W92">
-        <v>0.2351065285384735</v>
+        <v>0.2351141491039848</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.01960620473640073</v>
+        <v>0.01939075193709972</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2667631385823995</v>
+        <v>0.2686631385823995</v>
       </c>
       <c r="C93">
-        <v>-274.8122074723037</v>
+        <v>-281.4026057940958</v>
       </c>
       <c r="D93">
-        <v>195.2617925276963</v>
+        <v>193.9053942059042</v>
       </c>
       <c r="E93">
-        <v>341.794</v>
+        <v>347.028</v>
       </c>
       <c r="F93">
-        <v>476.294</v>
+        <v>481.528</v>
       </c>
       <c r="G93">
         <v>6.22</v>
@@ -8913,37 +8913,37 @@
         <v>2.177777777777806</v>
       </c>
       <c r="M93">
-        <v>112.3101252</v>
+        <v>113.5443024</v>
       </c>
       <c r="N93">
-        <v>-110.1323474222222</v>
+        <v>-111.3665246222222</v>
       </c>
       <c r="O93">
-        <v>-16.51985211333333</v>
+        <v>-16.70497869333333</v>
       </c>
       <c r="P93">
-        <v>-93.61249530888887</v>
+        <v>-94.66154592888887</v>
       </c>
       <c r="Q93">
-        <v>78.98750469111113</v>
+        <v>77.93845407111112</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.5867695877530373</v>
+        <v>0.6543907862221672</v>
       </c>
       <c r="T93">
-        <v>7.050647221561994</v>
+        <v>7.931978124257245</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.00290861279056495</v>
+        <v>0.002876997434145765</v>
       </c>
       <c r="W93">
-        <v>0.2351141491039848</v>
+        <v>0.2351216040050285</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.01939075193709972</v>
+        <v>0.01917998289430511</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2686631385823995</v>
+        <v>0.2705631385823995</v>
       </c>
       <c r="C94">
-        <v>-281.4026057940958</v>
+        <v>-287.9742895056128</v>
       </c>
       <c r="D94">
-        <v>193.9053942059042</v>
+        <v>192.5677104943872</v>
       </c>
       <c r="E94">
-        <v>347.028</v>
+        <v>352.262</v>
       </c>
       <c r="F94">
-        <v>481.528</v>
+        <v>486.762</v>
       </c>
       <c r="G94">
         <v>6.22</v>
@@ -8995,37 +8995,37 @@
         <v>2.177777777777806</v>
       </c>
       <c r="M94">
-        <v>113.5443024</v>
+        <v>114.7784796</v>
       </c>
       <c r="N94">
-        <v>-111.3665246222222</v>
+        <v>-112.6007018222222</v>
       </c>
       <c r="O94">
-        <v>-16.70497869333333</v>
+        <v>-16.89010527333333</v>
       </c>
       <c r="P94">
-        <v>-94.66154592888887</v>
+        <v>-95.71059654888887</v>
       </c>
       <c r="Q94">
-        <v>77.93845407111112</v>
+        <v>76.88940345111112</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.6543907862221672</v>
+        <v>0.7413323271110482</v>
       </c>
       <c r="T94">
-        <v>7.931978124257245</v>
+        <v>9.065117856293995</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.002876997434145765</v>
+        <v>0.002846061977864628</v>
       </c>
       <c r="W94">
-        <v>0.2351216040050285</v>
+        <v>0.2351288985856195</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.01917998289430511</v>
+        <v>0.01897374651909756</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2705631385823995</v>
+        <v>0.2724631385823995</v>
       </c>
       <c r="C95">
-        <v>-287.9742895056128</v>
+        <v>-294.5276432693423</v>
       </c>
       <c r="D95">
-        <v>192.5677104943872</v>
+        <v>191.2483567306577</v>
       </c>
       <c r="E95">
-        <v>352.262</v>
+        <v>357.496</v>
       </c>
       <c r="F95">
-        <v>486.762</v>
+        <v>491.996</v>
       </c>
       <c r="G95">
         <v>6.22</v>
@@ -9077,37 +9077,37 @@
         <v>2.177777777777806</v>
       </c>
       <c r="M95">
-        <v>114.7784796</v>
+        <v>116.0126568</v>
       </c>
       <c r="N95">
-        <v>-112.6007018222222</v>
+        <v>-113.8348790222222</v>
       </c>
       <c r="O95">
-        <v>-16.89010527333333</v>
+        <v>-17.07523185333333</v>
       </c>
       <c r="P95">
-        <v>-95.71059654888887</v>
+        <v>-96.75964716888888</v>
       </c>
       <c r="Q95">
-        <v>76.88940345111112</v>
+        <v>75.84035283111112</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.7413323271110482</v>
+        <v>0.8572543816295563</v>
       </c>
       <c r="T95">
-        <v>9.065117856293995</v>
+        <v>10.57597083234299</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.002846061977864628</v>
+        <v>0.002815784722780961</v>
       </c>
       <c r="W95">
-        <v>0.2351288985856195</v>
+        <v>0.2351360379623683</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.01897374651909756</v>
+        <v>0.01877189815187308</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2724631385823995</v>
+        <v>0.2743631385823995</v>
       </c>
       <c r="C96">
-        <v>-294.5276432693423</v>
+        <v>-301.0630412776374</v>
       </c>
       <c r="D96">
-        <v>191.2483567306577</v>
+        <v>189.9469587223627</v>
       </c>
       <c r="E96">
-        <v>357.496</v>
+        <v>362.73</v>
       </c>
       <c r="F96">
-        <v>491.996</v>
+        <v>497.23</v>
       </c>
       <c r="G96">
         <v>6.22</v>
@@ -9159,37 +9159,37 @@
         <v>2.177777777777806</v>
       </c>
       <c r="M96">
-        <v>116.0126568</v>
+        <v>117.246834</v>
       </c>
       <c r="N96">
-        <v>-113.8348790222222</v>
+        <v>-115.0690562222222</v>
       </c>
       <c r="O96">
-        <v>-17.07523185333333</v>
+        <v>-17.26035843333333</v>
       </c>
       <c r="P96">
-        <v>-96.75964716888888</v>
+        <v>-97.80869778888888</v>
       </c>
       <c r="Q96">
-        <v>75.84035283111112</v>
+        <v>74.79130221111112</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.8572543816295563</v>
+        <v>1.019545257955468</v>
       </c>
       <c r="T96">
-        <v>10.57597083234299</v>
+        <v>12.6911649988116</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.002815784722780961</v>
+        <v>0.002786144883593793</v>
       </c>
       <c r="W96">
-        <v>0.2351360379623683</v>
+        <v>0.2351430270364486</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.01877189815187308</v>
+        <v>0.01857429922395859</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2743631385823995</v>
+        <v>0.2762631385823995</v>
       </c>
       <c r="C97">
-        <v>-301.0630412776374</v>
+        <v>-307.5808476065423</v>
       </c>
       <c r="D97">
-        <v>189.9469587223627</v>
+        <v>188.6631523934577</v>
       </c>
       <c r="E97">
-        <v>362.73</v>
+        <v>367.964</v>
       </c>
       <c r="F97">
-        <v>497.23</v>
+        <v>502.464</v>
       </c>
       <c r="G97">
         <v>6.22</v>
@@ -9241,37 +9241,37 @@
         <v>2.177777777777806</v>
       </c>
       <c r="M97">
-        <v>117.246834</v>
+        <v>118.4810112</v>
       </c>
       <c r="N97">
-        <v>-115.0690562222222</v>
+        <v>-116.3032334222222</v>
       </c>
       <c r="O97">
-        <v>-17.26035843333333</v>
+        <v>-17.44548501333333</v>
       </c>
       <c r="P97">
-        <v>-97.80869778888888</v>
+        <v>-98.85774840888887</v>
       </c>
       <c r="Q97">
-        <v>74.79130221111112</v>
+        <v>73.74225159111113</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.019545257955468</v>
+        <v>1.262981572444336</v>
       </c>
       <c r="T97">
-        <v>12.6911649988116</v>
+        <v>15.86395624851451</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.002786144883593793</v>
+        <v>0.002757122541056358</v>
       </c>
       <c r="W97">
-        <v>0.2351430270364486</v>
+        <v>0.2351498705048189</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.01857429922395859</v>
+        <v>0.01838081694037574</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2762631385823995</v>
+        <v>0.2781631385823995</v>
       </c>
       <c r="C98">
-        <v>-307.5808476065422</v>
+        <v>-314.0814165553667</v>
       </c>
       <c r="D98">
-        <v>188.6631523934577</v>
+        <v>187.3965834446333</v>
       </c>
       <c r="E98">
-        <v>367.9639999999999</v>
+        <v>373.198</v>
       </c>
       <c r="F98">
-        <v>502.4639999999999</v>
+        <v>507.698</v>
       </c>
       <c r="G98">
         <v>6.22</v>
@@ -9323,37 +9323,37 @@
         <v>2.177777777777806</v>
       </c>
       <c r="M98">
-        <v>118.4810112</v>
+        <v>119.7151884</v>
       </c>
       <c r="N98">
-        <v>-116.3032334222222</v>
+        <v>-117.5374106222222</v>
       </c>
       <c r="O98">
-        <v>-17.44548501333333</v>
+        <v>-17.63061159333333</v>
       </c>
       <c r="P98">
-        <v>-98.85774840888887</v>
+        <v>-99.90679902888887</v>
       </c>
       <c r="Q98">
-        <v>73.74225159111113</v>
+        <v>72.69320097111112</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.262981572444333</v>
+        <v>1.66870876325911</v>
       </c>
       <c r="T98">
-        <v>15.86395624851447</v>
+        <v>21.15194166468596</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.002757122541056358</v>
+        <v>0.002728698597334127</v>
       </c>
       <c r="W98">
-        <v>0.2351498705048189</v>
+        <v>0.2351565728707486</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.01838081694037574</v>
+        <v>0.01819132398222756</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2781631385823995</v>
+        <v>0.2800631385823995</v>
       </c>
       <c r="C99">
-        <v>-314.0814165553667</v>
+        <v>-320.5650929726718</v>
       </c>
       <c r="D99">
-        <v>187.3965834446333</v>
+        <v>186.1469070273282</v>
       </c>
       <c r="E99">
-        <v>373.198</v>
+        <v>378.432</v>
       </c>
       <c r="F99">
-        <v>507.698</v>
+        <v>512.932</v>
       </c>
       <c r="G99">
         <v>6.22</v>
@@ -9405,37 +9405,37 @@
         <v>2.177777777777806</v>
       </c>
       <c r="M99">
-        <v>119.7151884</v>
+        <v>120.9493656</v>
       </c>
       <c r="N99">
-        <v>-117.5374106222222</v>
+        <v>-118.7715878222222</v>
       </c>
       <c r="O99">
-        <v>-17.63061159333333</v>
+        <v>-17.81573817333333</v>
       </c>
       <c r="P99">
-        <v>-99.90679902888887</v>
+        <v>-100.9558496488889</v>
       </c>
       <c r="Q99">
-        <v>72.69320097111112</v>
+        <v>71.64415035111112</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.66870876325911</v>
+        <v>2.480163144888665</v>
       </c>
       <c r="T99">
-        <v>21.15194166468596</v>
+        <v>31.72791249702894</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.002728698597334127</v>
+        <v>0.002700854734096024</v>
       </c>
       <c r="W99">
-        <v>0.2351565728707486</v>
+        <v>0.2351631384537002</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.01819132398222756</v>
+        <v>0.0180056982273068</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2800631385823995</v>
+        <v>0.2819631385823995</v>
       </c>
       <c r="C100">
-        <v>-320.5650929726718</v>
+        <v>-327.0322125692998</v>
       </c>
       <c r="D100">
-        <v>186.1469070273282</v>
+        <v>184.9137874307002</v>
       </c>
       <c r="E100">
-        <v>378.432</v>
+        <v>383.6659999999999</v>
       </c>
       <c r="F100">
-        <v>512.932</v>
+        <v>518.1659999999999</v>
       </c>
       <c r="G100">
         <v>6.22</v>
@@ -9487,37 +9487,37 @@
         <v>2.177777777777806</v>
       </c>
       <c r="M100">
-        <v>120.9493656</v>
+        <v>122.1835428</v>
       </c>
       <c r="N100">
-        <v>-118.7715878222222</v>
+        <v>-120.0057650222222</v>
       </c>
       <c r="O100">
-        <v>-17.81573817333333</v>
+        <v>-18.00086475333333</v>
       </c>
       <c r="P100">
-        <v>-100.9558496488889</v>
+        <v>-102.0049002688889</v>
       </c>
       <c r="Q100">
-        <v>71.64415035111112</v>
+        <v>70.59509973111113</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.480163144888665</v>
+        <v>4.914526289777331</v>
       </c>
       <c r="T100">
-        <v>31.72791249702894</v>
+        <v>63.45582499405787</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.002700854734096024</v>
+        <v>0.002673573373145559</v>
       </c>
       <c r="W100">
-        <v>0.2351631384537002</v>
+        <v>0.2351695713986123</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.0180056982273068</v>
+        <v>0.01782382248763703</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2819631385823995</v>
-      </c>
-      <c r="C101">
-        <v>-327.0322125692998</v>
-      </c>
-      <c r="D101">
-        <v>184.9137874307002</v>
-      </c>
-      <c r="E101">
-        <v>383.6659999999999</v>
-      </c>
-      <c r="F101">
-        <v>518.1659999999999</v>
-      </c>
-      <c r="G101">
-        <v>6.22</v>
-      </c>
-      <c r="H101">
-        <v>388.9</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>174.7777777777778</v>
-      </c>
-      <c r="K101">
-        <v>172.6</v>
-      </c>
-      <c r="L101">
-        <v>2.177777777777806</v>
-      </c>
-      <c r="M101">
-        <v>122.1835428</v>
-      </c>
-      <c r="N101">
-        <v>-120.0057650222222</v>
-      </c>
-      <c r="O101">
-        <v>-18.00086475333333</v>
-      </c>
-      <c r="P101">
-        <v>-102.0049002688889</v>
-      </c>
-      <c r="Q101">
-        <v>70.59509973111113</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>4.914526289777331</v>
-      </c>
-      <c r="T101">
-        <v>63.45582499405787</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.002673573373145559</v>
-      </c>
-      <c r="W101">
-        <v>0.2351695713986123</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.01782382248763703</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
